--- a/final_report/GitHub_Dashboard_12_Quarters_Master.xlsx
+++ b/final_report/GitHub_Dashboard_12_Quarters_Master.xlsx
@@ -1373,7 +1373,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>03-Jul-2024 (Wed)</t>
+          <t>10-Jul-2024 (Wed)</t>
         </is>
       </c>
       <c r="G5" s="15" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>16-Jul-2024 (Tue)</t>
+          <t>19-Jul-2024 (Fri)</t>
         </is>
       </c>
       <c r="J5" s="15" t="n">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>06-Sep-2024 (Fri)</t>
+          <t>10-Sep-2024 (Tue)</t>
         </is>
       </c>
       <c r="G6" s="15" t="n">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>17-Sep-2024 (Tue)</t>
+          <t>18-Sep-2024 (Wed)</t>
         </is>
       </c>
       <c r="J6" s="15" t="n">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>01-Aug-2024 (Thu)</t>
+          <t>07-Aug-2024 (Wed)</t>
         </is>
       </c>
       <c r="G7" s="15" t="n">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>14-Aug-2024 (Wed)</t>
+          <t>16-Aug-2024 (Fri)</t>
         </is>
       </c>
       <c r="J7" s="15" t="n">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>05-Jul-2024 (Fri)</t>
+          <t>08-Jul-2024 (Mon)</t>
         </is>
       </c>
       <c r="G8" s="15" t="n">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>15-Jul-2024 (Mon)</t>
+          <t>16-Jul-2024 (Tue)</t>
         </is>
       </c>
       <c r="J8" s="15" t="n">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>04-Sep-2024 (Wed)</t>
+          <t>10-Sep-2024 (Tue)</t>
         </is>
       </c>
       <c r="G10" s="15" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>16-Sep-2024 (Mon)</t>
+          <t>18-Sep-2024 (Wed)</t>
         </is>
       </c>
       <c r="J10" s="15" t="n">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>13-Sep-2024 (Fri)</t>
+          <t>20-Sep-2024 (Fri)</t>
         </is>
       </c>
       <c r="G11" s="15" t="n">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>01-Oct-2024 (Tue)</t>
+          <t>30-Sep-2024 (Mon)</t>
         </is>
       </c>
       <c r="J11" s="15" t="n">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>10-Sep-2024 (Tue)</t>
+          <t>11-Sep-2024 (Wed)</t>
         </is>
       </c>
       <c r="G12" s="15" t="n">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>18-Sep-2024 (Wed)</t>
+          <t>19-Sep-2024 (Thu)</t>
         </is>
       </c>
       <c r="J12" s="15" t="n">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>04-Sep-2024 (Wed)</t>
+          <t>10-Sep-2024 (Tue)</t>
         </is>
       </c>
       <c r="G13" s="15" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>25-Sep-2024 (Wed)</t>
+          <t>24-Sep-2024 (Tue)</t>
         </is>
       </c>
       <c r="J14" s="15" t="n">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>09-Sep-2024 (Mon)</t>
+          <t>16-Sep-2024 (Mon)</t>
         </is>
       </c>
       <c r="G15" s="15" t="n">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>20-Sep-2024 (Fri)</t>
+          <t>24-Sep-2024 (Tue)</t>
         </is>
       </c>
       <c r="J15" s="15" t="n">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>14-Aug-2024 (Wed)</t>
+          <t>16-Aug-2024 (Fri)</t>
         </is>
       </c>
       <c r="G16" s="15" t="n">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>27-Aug-2024 (Tue)</t>
+          <t>26-Aug-2024 (Mon)</t>
         </is>
       </c>
       <c r="J16" s="15" t="n">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>16-Aug-2024 (Fri)</t>
+          <t>21-Aug-2024 (Wed)</t>
         </is>
       </c>
       <c r="G17" s="15" t="n">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>30-Aug-2024 (Fri)</t>
+          <t>29-Aug-2024 (Thu)</t>
         </is>
       </c>
       <c r="J17" s="15" t="n">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>25-Sep-2024 (Wed)</t>
+          <t>24-Sep-2024 (Tue)</t>
         </is>
       </c>
       <c r="J19" s="15" t="n">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>22-Jul-2024 (Mon)</t>
+          <t>19-Jul-2024 (Fri)</t>
         </is>
       </c>
       <c r="J20" s="15" t="n">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>08-Jul-2024 (Mon)</t>
+          <t>10-Jul-2024 (Wed)</t>
         </is>
       </c>
       <c r="G21" s="15" t="n">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>16-Jul-2024 (Tue)</t>
+          <t>19-Jul-2024 (Fri)</t>
         </is>
       </c>
       <c r="J21" s="15" t="n">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>07-Aug-2024 (Wed)</t>
+          <t>13-Aug-2024 (Tue)</t>
         </is>
       </c>
       <c r="G23" s="15" t="n">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>06-Sep-2024 (Fri)</t>
+          <t>11-Sep-2024 (Wed)</t>
         </is>
       </c>
       <c r="G26" s="15" t="n">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>18-Sep-2024 (Wed)</t>
+          <t>19-Sep-2024 (Thu)</t>
         </is>
       </c>
       <c r="J26" s="15" t="n">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>11-Jul-2024 (Thu)</t>
+          <t>18-Jul-2024 (Thu)</t>
         </is>
       </c>
       <c r="G27" s="15" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>24-Jul-2024 (Wed)</t>
+          <t>26-Jul-2024 (Fri)</t>
         </is>
       </c>
       <c r="J27" s="15" t="n">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>11-Jul-2024 (Thu)</t>
+          <t>18-Jul-2024 (Thu)</t>
         </is>
       </c>
       <c r="G28" s="15" t="n">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>24-Jul-2024 (Wed)</t>
+          <t>26-Jul-2024 (Fri)</t>
         </is>
       </c>
       <c r="J28" s="15" t="n">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>06-Sep-2024 (Fri)</t>
+          <t>10-Sep-2024 (Tue)</t>
         </is>
       </c>
       <c r="G29" s="15" t="n">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>13-Sep-2024 (Fri)</t>
+          <t>18-Sep-2024 (Wed)</t>
         </is>
       </c>
       <c r="J29" s="15" t="n">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>05-Jul-2024 (Fri)</t>
+          <t>08-Jul-2024 (Mon)</t>
         </is>
       </c>
       <c r="G30" s="15" t="n">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>18-Jul-2024 (Thu)</t>
+          <t>16-Jul-2024 (Tue)</t>
         </is>
       </c>
       <c r="J30" s="15" t="n">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>10-Sep-2024 (Tue)</t>
+          <t>11-Sep-2024 (Wed)</t>
         </is>
       </c>
       <c r="G31" s="15" t="n">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>16-Sep-2024 (Mon)</t>
+          <t>19-Sep-2024 (Thu)</t>
         </is>
       </c>
       <c r="J31" s="15" t="n">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>10-Sep-2024 (Tue)</t>
+          <t>11-Sep-2024 (Wed)</t>
         </is>
       </c>
       <c r="G32" s="15" t="n">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>20-Sep-2024 (Fri)</t>
+          <t>19-Sep-2024 (Thu)</t>
         </is>
       </c>
       <c r="J32" s="15" t="n">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>30-Aug-2024 (Fri)</t>
+          <t>29-Aug-2024 (Thu)</t>
         </is>
       </c>
       <c r="J33" s="15" t="n">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>07-Aug-2024 (Wed)</t>
+          <t>13-Aug-2024 (Tue)</t>
         </is>
       </c>
       <c r="G34" s="15" t="n">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>20-Aug-2024 (Tue)</t>
+          <t>22-Aug-2024 (Thu)</t>
         </is>
       </c>
       <c r="J34" s="15" t="n">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>08-Jul-2024 (Mon)</t>
+          <t>12-Jul-2024 (Fri)</t>
         </is>
       </c>
       <c r="G35" s="15" t="n">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>22-Jul-2024 (Mon)</t>
+          <t>23-Jul-2024 (Tue)</t>
         </is>
       </c>
       <c r="J35" s="15" t="n">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>17-Sep-2024 (Tue)</t>
+          <t>18-Sep-2024 (Wed)</t>
         </is>
       </c>
       <c r="G36" s="15" t="n">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>24-Sep-2024 (Tue)</t>
+          <t>26-Sep-2024 (Thu)</t>
         </is>
       </c>
       <c r="J36" s="15" t="n">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>11-Sep-2024 (Wed)</t>
+          <t>16-Sep-2024 (Mon)</t>
         </is>
       </c>
       <c r="G38" s="15" t="n">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>25-Sep-2024 (Wed)</t>
+          <t>24-Sep-2024 (Tue)</t>
         </is>
       </c>
       <c r="J38" s="15" t="n">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>12-Sep-2024 (Thu)</t>
+          <t>16-Sep-2024 (Mon)</t>
         </is>
       </c>
       <c r="G39" s="15" t="n">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>20-Sep-2024 (Fri)</t>
+          <t>24-Sep-2024 (Tue)</t>
         </is>
       </c>
       <c r="J39" s="15" t="n">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>15-Jul-2024 (Mon)</t>
+          <t>18-Jul-2024 (Thu)</t>
         </is>
       </c>
       <c r="G40" s="15" t="n">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>25-Jul-2024 (Thu)</t>
+          <t>26-Jul-2024 (Fri)</t>
         </is>
       </c>
       <c r="J40" s="15" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>14-Aug-2024 (Wed)</t>
+          <t>16-Aug-2024 (Fri)</t>
         </is>
       </c>
       <c r="G41" s="15" t="n">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>21-Aug-2024 (Wed)</t>
+          <t>26-Aug-2024 (Mon)</t>
         </is>
       </c>
       <c r="J41" s="15" t="n">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>03-Jul-2024 (Wed)</t>
+          <t>08-Jul-2024 (Mon)</t>
         </is>
       </c>
       <c r="G42" s="15" t="n">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>15-Jul-2024 (Mon)</t>
+          <t>16-Jul-2024 (Tue)</t>
         </is>
       </c>
       <c r="J42" s="15" t="n">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>09-Aug-2024 (Fri)</t>
+          <t>13-Aug-2024 (Tue)</t>
         </is>
       </c>
       <c r="G43" s="15" t="n">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>19-Aug-2024 (Mon)</t>
+          <t>22-Aug-2024 (Thu)</t>
         </is>
       </c>
       <c r="J43" s="15" t="n">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>22-Jul-2024 (Mon)</t>
+          <t>19-Jul-2024 (Fri)</t>
         </is>
       </c>
       <c r="J44" s="15" t="n">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>10-Jul-2024 (Wed)</t>
+          <t>12-Jul-2024 (Fri)</t>
         </is>
       </c>
       <c r="G45" s="15" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>24-Jul-2024 (Wed)</t>
+          <t>23-Jul-2024 (Tue)</t>
         </is>
       </c>
       <c r="J45" s="15" t="n">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>06-Aug-2024 (Tue)</t>
+          <t>07-Aug-2024 (Wed)</t>
         </is>
       </c>
       <c r="G46" s="15" t="n">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>13-Aug-2024 (Tue)</t>
+          <t>16-Aug-2024 (Fri)</t>
         </is>
       </c>
       <c r="J46" s="15" t="n">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>04-Sep-2024 (Wed)</t>
+          <t>10-Sep-2024 (Tue)</t>
         </is>
       </c>
       <c r="G47" s="15" t="n">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>14-Aug-2024 (Wed)</t>
+          <t>16-Aug-2024 (Fri)</t>
         </is>
       </c>
       <c r="G48" s="15" t="n">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>21-Aug-2024 (Wed)</t>
+          <t>26-Aug-2024 (Mon)</t>
         </is>
       </c>
       <c r="J48" s="15" t="n">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>11-Jul-2024 (Thu)</t>
+          <t>18-Jul-2024 (Thu)</t>
         </is>
       </c>
       <c r="G49" s="15" t="n">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>24-Jul-2024 (Wed)</t>
+          <t>26-Jul-2024 (Fri)</t>
         </is>
       </c>
       <c r="J49" s="15" t="n">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>06-Aug-2024 (Tue)</t>
+          <t>07-Aug-2024 (Wed)</t>
         </is>
       </c>
       <c r="G50" s="15" t="n">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>13-Aug-2024 (Tue)</t>
+          <t>16-Aug-2024 (Fri)</t>
         </is>
       </c>
       <c r="J50" s="15" t="n">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>05-Aug-2024 (Mon)</t>
+          <t>07-Aug-2024 (Wed)</t>
         </is>
       </c>
       <c r="G51" s="15" t="n">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>19-Aug-2024 (Mon)</t>
+          <t>16-Aug-2024 (Fri)</t>
         </is>
       </c>
       <c r="J51" s="15" t="n">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>10-Sep-2024 (Tue)</t>
+          <t>11-Sep-2024 (Wed)</t>
         </is>
       </c>
       <c r="G53" s="15" t="n">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>18-Sep-2024 (Wed)</t>
+          <t>19-Sep-2024 (Thu)</t>
         </is>
       </c>
       <c r="J53" s="15" t="n">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>10-Jul-2024 (Wed)</t>
+          <t>12-Jul-2024 (Fri)</t>
         </is>
       </c>
       <c r="G54" s="15" t="n">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>24-Jul-2024 (Wed)</t>
+          <t>23-Jul-2024 (Tue)</t>
         </is>
       </c>
       <c r="J54" s="15" t="n">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>08-Apr-2024 (Mon)</t>
+          <t>09-Apr-2024 (Tue)</t>
         </is>
       </c>
       <c r="G5" s="15" t="n">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>15-Apr-2024 (Mon)</t>
+          <t>19-Apr-2024 (Fri)</t>
         </is>
       </c>
       <c r="J5" s="15" t="n">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>30-Apr-2024 (Tue)</t>
+          <t>08-May-2024 (Wed)</t>
         </is>
       </c>
       <c r="G6" s="15" t="n">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>14-May-2024 (Tue)</t>
+          <t>16-May-2024 (Thu)</t>
         </is>
       </c>
       <c r="J6" s="15" t="n">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>04-Apr-2024 (Thu)</t>
+          <t>08-Apr-2024 (Mon)</t>
         </is>
       </c>
       <c r="G7" s="15" t="n">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>16-Apr-2024 (Tue)</t>
+          <t>18-Apr-2024 (Thu)</t>
         </is>
       </c>
       <c r="J7" s="15" t="n">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>12-Jun-2024 (Wed)</t>
+          <t>13-Jun-2024 (Thu)</t>
         </is>
       </c>
       <c r="G8" s="15" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>19-Jun-2024 (Wed)</t>
+          <t>24-Jun-2024 (Mon)</t>
         </is>
       </c>
       <c r="J8" s="15" t="n">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>05-Jun-2024 (Wed)</t>
+          <t>10-Jun-2024 (Mon)</t>
         </is>
       </c>
       <c r="G10" s="15" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>10-Jun-2024 (Mon)</t>
+          <t>12-Jun-2024 (Wed)</t>
         </is>
       </c>
       <c r="G12" s="15" t="n">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>20-Jun-2024 (Thu)</t>
+          <t>21-Jun-2024 (Fri)</t>
         </is>
       </c>
       <c r="J12" s="15" t="n">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>09-May-2024 (Thu)</t>
+          <t>16-May-2024 (Thu)</t>
         </is>
       </c>
       <c r="G13" s="15" t="n">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>22-May-2024 (Wed)</t>
+          <t>24-May-2024 (Fri)</t>
         </is>
       </c>
       <c r="J13" s="15" t="n">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>17-May-2024 (Fri)</t>
+          <t>21-May-2024 (Tue)</t>
         </is>
       </c>
       <c r="G14" s="15" t="n">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>30-May-2024 (Thu)</t>
+          <t>29-May-2024 (Wed)</t>
         </is>
       </c>
       <c r="J14" s="15" t="n">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>12-Jun-2024 (Wed)</t>
+          <t>13-Jun-2024 (Thu)</t>
         </is>
       </c>
       <c r="G15" s="15" t="n">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>21-Jun-2024 (Fri)</t>
+          <t>24-Jun-2024 (Mon)</t>
         </is>
       </c>
       <c r="J15" s="15" t="n">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>04-Apr-2024 (Thu)</t>
+          <t>09-Apr-2024 (Tue)</t>
         </is>
       </c>
       <c r="G16" s="15" t="n">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>18-Apr-2024 (Thu)</t>
+          <t>19-Apr-2024 (Fri)</t>
         </is>
       </c>
       <c r="J16" s="15" t="n">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>18-Jun-2024 (Tue)</t>
+          <t>20-Jun-2024 (Thu)</t>
         </is>
       </c>
       <c r="G17" s="15" t="n">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>01-Jul-2024 (Mon)</t>
+          <t>28-Jun-2024 (Fri)</t>
         </is>
       </c>
       <c r="J17" s="15" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>06-Jun-2024 (Thu)</t>
+          <t>12-Jun-2024 (Wed)</t>
         </is>
       </c>
       <c r="G18" s="15" t="n">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>12-Jun-2024 (Wed)</t>
+          <t>13-Jun-2024 (Thu)</t>
         </is>
       </c>
       <c r="G19" s="15" t="n">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>21-Jun-2024 (Fri)</t>
+          <t>24-Jun-2024 (Mon)</t>
         </is>
       </c>
       <c r="J19" s="15" t="n">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>06-Jun-2024 (Thu)</t>
+          <t>12-Jun-2024 (Wed)</t>
         </is>
       </c>
       <c r="G20" s="15" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>19-Jun-2024 (Wed)</t>
+          <t>21-Jun-2024 (Fri)</t>
         </is>
       </c>
       <c r="J20" s="15" t="n">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>13-Jun-2024 (Thu)</t>
+          <t>19-Jun-2024 (Wed)</t>
         </is>
       </c>
       <c r="J22" s="15" t="n">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>08-May-2024 (Wed)</t>
+          <t>15-May-2024 (Wed)</t>
         </is>
       </c>
       <c r="G23" s="15" t="n">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>27-May-2024 (Mon)</t>
+          <t>23-May-2024 (Thu)</t>
         </is>
       </c>
       <c r="J23" s="15" t="n">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>07-May-2024 (Tue)</t>
+          <t>10-May-2024 (Fri)</t>
         </is>
       </c>
       <c r="G24" s="15" t="n">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>16-May-2024 (Thu)</t>
+          <t>20-May-2024 (Mon)</t>
         </is>
       </c>
       <c r="J24" s="15" t="n">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>14-Jun-2024 (Fri)</t>
+          <t>19-Jun-2024 (Wed)</t>
         </is>
       </c>
       <c r="G25" s="15" t="n">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>25-Jun-2024 (Tue)</t>
+          <t>27-Jun-2024 (Thu)</t>
         </is>
       </c>
       <c r="J25" s="15" t="n">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>17-May-2024 (Fri)</t>
+          <t>21-May-2024 (Tue)</t>
         </is>
       </c>
       <c r="G26" s="15" t="n">
@@ -6785,7 +6785,7 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>28-May-2024 (Tue)</t>
+          <t>29-May-2024 (Wed)</t>
         </is>
       </c>
       <c r="J26" s="15" t="n">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>21-May-2024 (Tue)</t>
+          <t>23-May-2024 (Thu)</t>
         </is>
       </c>
       <c r="J27" s="15" t="n">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>08-Apr-2024 (Mon)</t>
+          <t>12-Apr-2024 (Fri)</t>
         </is>
       </c>
       <c r="G28" s="15" t="n">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>24-Apr-2024 (Wed)</t>
+          <t>23-Apr-2024 (Tue)</t>
         </is>
       </c>
       <c r="J28" s="15" t="n">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>02-Apr-2024 (Tue)</t>
+          <t>08-Apr-2024 (Mon)</t>
         </is>
       </c>
       <c r="G29" s="15" t="n">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>15-Apr-2024 (Mon)</t>
+          <t>18-Apr-2024 (Thu)</t>
         </is>
       </c>
       <c r="J29" s="15" t="n">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>24-May-2024 (Fri)</t>
+          <t>23-May-2024 (Thu)</t>
         </is>
       </c>
       <c r="J31" s="15" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>12-Jun-2024 (Wed)</t>
+          <t>13-Jun-2024 (Thu)</t>
         </is>
       </c>
       <c r="G32" s="15" t="n">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>25-Jun-2024 (Tue)</t>
+          <t>24-Jun-2024 (Mon)</t>
         </is>
       </c>
       <c r="J32" s="15" t="n">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>08-Apr-2024 (Mon)</t>
+          <t>09-Apr-2024 (Tue)</t>
         </is>
       </c>
       <c r="G33" s="15" t="n">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>18-Apr-2024 (Thu)</t>
+          <t>19-Apr-2024 (Fri)</t>
         </is>
       </c>
       <c r="J33" s="15" t="n">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>06-May-2024 (Mon)</t>
+          <t>08-May-2024 (Wed)</t>
         </is>
       </c>
       <c r="G34" s="15" t="n">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>14-May-2024 (Tue)</t>
+          <t>16-May-2024 (Thu)</t>
         </is>
       </c>
       <c r="J34" s="15" t="n">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>02-Apr-2024 (Tue)</t>
+          <t>08-Apr-2024 (Mon)</t>
         </is>
       </c>
       <c r="G35" s="15" t="n">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>03-Jun-2024 (Mon)</t>
+          <t>10-Jun-2024 (Mon)</t>
         </is>
       </c>
       <c r="G36" s="15" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>20-Jun-2024 (Thu)</t>
+          <t>19-Jun-2024 (Wed)</t>
         </is>
       </c>
       <c r="J36" s="15" t="n">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>13-May-2024 (Mon)</t>
+          <t>16-May-2024 (Thu)</t>
         </is>
       </c>
       <c r="G38" s="15" t="n">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>21-May-2024 (Tue)</t>
+          <t>24-May-2024 (Fri)</t>
         </is>
       </c>
       <c r="J38" s="15" t="n">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>22-May-2024 (Wed)</t>
+          <t>21-May-2024 (Tue)</t>
         </is>
       </c>
       <c r="J39" s="15" t="n">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>04-Apr-2024 (Thu)</t>
+          <t>12-Apr-2024 (Fri)</t>
         </is>
       </c>
       <c r="G40" s="15" t="n">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>19-Apr-2024 (Fri)</t>
+          <t>23-Apr-2024 (Tue)</t>
         </is>
       </c>
       <c r="J40" s="15" t="n">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>08-Apr-2024 (Mon)</t>
+          <t>09-Apr-2024 (Tue)</t>
         </is>
       </c>
       <c r="G42" s="15" t="n">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>18-Apr-2024 (Thu)</t>
+          <t>19-Apr-2024 (Fri)</t>
         </is>
       </c>
       <c r="J42" s="15" t="n">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>09-Apr-2024 (Tue)</t>
+          <t>12-Apr-2024 (Fri)</t>
         </is>
       </c>
       <c r="G43" s="15" t="n">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>19-Apr-2024 (Fri)</t>
+          <t>23-Apr-2024 (Tue)</t>
         </is>
       </c>
       <c r="J43" s="15" t="n">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>10-Jun-2024 (Mon)</t>
+          <t>13-Jun-2024 (Thu)</t>
         </is>
       </c>
       <c r="G44" s="15" t="n">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>21-Jun-2024 (Fri)</t>
+          <t>24-Jun-2024 (Mon)</t>
         </is>
       </c>
       <c r="J44" s="15" t="n">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>10-Jun-2024 (Mon)</t>
+          <t>12-Jun-2024 (Wed)</t>
         </is>
       </c>
       <c r="G45" s="15" t="n">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>18-Jun-2024 (Tue)</t>
+          <t>21-Jun-2024 (Fri)</t>
         </is>
       </c>
       <c r="J45" s="15" t="n">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>08-Apr-2024 (Mon)</t>
+          <t>12-Apr-2024 (Fri)</t>
         </is>
       </c>
       <c r="G46" s="15" t="n">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>24-Apr-2024 (Wed)</t>
+          <t>23-Apr-2024 (Tue)</t>
         </is>
       </c>
       <c r="J46" s="15" t="n">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>13-May-2024 (Mon)</t>
+          <t>16-May-2024 (Thu)</t>
         </is>
       </c>
       <c r="G47" s="15" t="n">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>21-May-2024 (Tue)</t>
+          <t>24-May-2024 (Fri)</t>
         </is>
       </c>
       <c r="J47" s="15" t="n">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>08-Apr-2024 (Mon)</t>
+          <t>12-Apr-2024 (Fri)</t>
         </is>
       </c>
       <c r="G48" s="15" t="n">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>24-Apr-2024 (Wed)</t>
+          <t>23-Apr-2024 (Tue)</t>
         </is>
       </c>
       <c r="J48" s="15" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>03-May-2024 (Fri)</t>
+          <t>08-May-2024 (Wed)</t>
         </is>
       </c>
       <c r="G49" s="15" t="n">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>17-May-2024 (Fri)</t>
+          <t>16-May-2024 (Thu)</t>
         </is>
       </c>
       <c r="J49" s="15" t="n">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>12-Apr-2024 (Fri)</t>
+          <t>18-Apr-2024 (Thu)</t>
         </is>
       </c>
       <c r="G50" s="15" t="n">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>10-Jun-2024 (Mon)</t>
+          <t>12-Jun-2024 (Wed)</t>
         </is>
       </c>
       <c r="G51" s="15" t="n">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>20-Jun-2024 (Thu)</t>
+          <t>21-Jun-2024 (Fri)</t>
         </is>
       </c>
       <c r="J51" s="15" t="n">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>06-May-2024 (Mon)</t>
+          <t>08-May-2024 (Wed)</t>
         </is>
       </c>
       <c r="G53" s="15" t="n">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>14-May-2024 (Tue)</t>
+          <t>16-May-2024 (Thu)</t>
         </is>
       </c>
       <c r="J53" s="15" t="n">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>03-Jun-2024 (Mon)</t>
+          <t>10-Jun-2024 (Mon)</t>
         </is>
       </c>
       <c r="G54" s="15" t="n">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>20-Jun-2024 (Thu)</t>
+          <t>19-Jun-2024 (Wed)</t>
         </is>
       </c>
       <c r="J54" s="15" t="n">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>01-Mar-2024 (Fri)</t>
+          <t>07-Mar-2024 (Thu)</t>
         </is>
       </c>
       <c r="G5" s="15" t="n">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>15-Mar-2024 (Fri)</t>
+          <t>18-Mar-2024 (Mon)</t>
         </is>
       </c>
       <c r="J5" s="15" t="n">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>04-Mar-2024 (Mon)</t>
+          <t>07-Mar-2024 (Thu)</t>
         </is>
       </c>
       <c r="G6" s="15" t="n">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>14-Mar-2024 (Thu)</t>
+          <t>18-Mar-2024 (Mon)</t>
         </is>
       </c>
       <c r="J6" s="15" t="n">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>12-Mar-2024 (Tue)</t>
+          <t>14-Mar-2024 (Thu)</t>
         </is>
       </c>
       <c r="G7" s="15" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>19-Mar-2024 (Tue)</t>
+          <t>22-Mar-2024 (Fri)</t>
         </is>
       </c>
       <c r="J7" s="15" t="n">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>12-Jan-2024 (Fri)</t>
+          <t>17-Jan-2024 (Wed)</t>
         </is>
       </c>
       <c r="G9" s="15" t="n">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>24-Jan-2024 (Wed)</t>
+          <t>29-Jan-2024 (Mon)</t>
         </is>
       </c>
       <c r="J9" s="15" t="n">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>08-Jan-2024 (Mon)</t>
+          <t>10-Jan-2024 (Wed)</t>
         </is>
       </c>
       <c r="G10" s="15" t="n">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>15-Jan-2024 (Mon)</t>
+          <t>18-Jan-2024 (Thu)</t>
         </is>
       </c>
       <c r="J10" s="15" t="n">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>15-Feb-2024 (Thu)</t>
+          <t>21-Feb-2024 (Wed)</t>
         </is>
       </c>
       <c r="G11" s="15" t="n">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>27-Feb-2024 (Tue)</t>
+          <t>29-Feb-2024 (Thu)</t>
         </is>
       </c>
       <c r="J11" s="15" t="n">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>04-Jan-2024 (Thu)</t>
+          <t>10-Jan-2024 (Wed)</t>
         </is>
       </c>
       <c r="G13" s="15" t="n">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>03-Jan-2024 (Wed)</t>
+          <t>08-Jan-2024 (Mon)</t>
         </is>
       </c>
       <c r="G14" s="15" t="n">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>06-Mar-2024 (Wed)</t>
+          <t>07-Mar-2024 (Thu)</t>
         </is>
       </c>
       <c r="G15" s="15" t="n">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>14-Mar-2024 (Thu)</t>
+          <t>18-Mar-2024 (Mon)</t>
         </is>
       </c>
       <c r="J15" s="15" t="n">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>05-Mar-2024 (Tue)</t>
+          <t>13-Mar-2024 (Wed)</t>
         </is>
       </c>
       <c r="G16" s="15" t="n">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>22-Mar-2024 (Fri)</t>
+          <t>21-Mar-2024 (Thu)</t>
         </is>
       </c>
       <c r="J16" s="15" t="n">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>13-Feb-2024 (Tue)</t>
+          <t>14-Feb-2024 (Wed)</t>
         </is>
       </c>
       <c r="G17" s="15" t="n">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>20-Feb-2024 (Tue)</t>
+          <t>22-Feb-2024 (Thu)</t>
         </is>
       </c>
       <c r="J17" s="15" t="n">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>12-Mar-2024 (Tue)</t>
+          <t>14-Mar-2024 (Thu)</t>
         </is>
       </c>
       <c r="G18" s="15" t="n">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>21-Mar-2024 (Thu)</t>
+          <t>22-Mar-2024 (Fri)</t>
         </is>
       </c>
       <c r="J18" s="15" t="n">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>06-Feb-2024 (Tue)</t>
+          <t>07-Feb-2024 (Wed)</t>
         </is>
       </c>
       <c r="G19" s="15" t="n">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>12-Feb-2024 (Mon)</t>
+          <t>15-Feb-2024 (Thu)</t>
         </is>
       </c>
       <c r="J19" s="15" t="n">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>12-Mar-2024 (Tue)</t>
+          <t>14-Mar-2024 (Thu)</t>
         </is>
       </c>
       <c r="G20" s="15" t="n">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>21-Mar-2024 (Thu)</t>
+          <t>22-Mar-2024 (Fri)</t>
         </is>
       </c>
       <c r="J20" s="15" t="n">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>21-Feb-2024 (Wed)</t>
+          <t>20-Feb-2024 (Tue)</t>
         </is>
       </c>
       <c r="J21" s="15" t="n">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>18-Mar-2024 (Mon)</t>
+          <t>21-Mar-2024 (Thu)</t>
         </is>
       </c>
       <c r="J22" s="15" t="n">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>07-Mar-2024 (Thu)</t>
+          <t>13-Mar-2024 (Wed)</t>
         </is>
       </c>
       <c r="G25" s="15" t="n">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>08-Jan-2024 (Mon)</t>
+          <t>10-Jan-2024 (Wed)</t>
         </is>
       </c>
       <c r="G26" s="15" t="n">
@@ -10630,7 +10630,7 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>17-Jan-2024 (Wed)</t>
+          <t>18-Jan-2024 (Thu)</t>
         </is>
       </c>
       <c r="J26" s="15" t="n">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>12-Feb-2024 (Mon)</t>
+          <t>14-Feb-2024 (Wed)</t>
         </is>
       </c>
       <c r="G27" s="15" t="n">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>23-Feb-2024 (Fri)</t>
+          <t>22-Feb-2024 (Thu)</t>
         </is>
       </c>
       <c r="J27" s="15" t="n">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>19-Feb-2024 (Mon)</t>
+          <t>21-Feb-2024 (Wed)</t>
         </is>
       </c>
       <c r="G28" s="15" t="n">
@@ -10778,7 +10778,7 @@
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>28-Feb-2024 (Wed)</t>
+          <t>29-Feb-2024 (Thu)</t>
         </is>
       </c>
       <c r="J28" s="15" t="n">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>14-Mar-2024 (Thu)</t>
+          <t>19-Mar-2024 (Tue)</t>
         </is>
       </c>
       <c r="G29" s="15" t="n">
@@ -10852,7 +10852,7 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>27-Mar-2024 (Wed)</t>
+          <t>28-Mar-2024 (Thu)</t>
         </is>
       </c>
       <c r="J29" s="15" t="n">
@@ -10913,7 +10913,7 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>15-Mar-2024 (Fri)</t>
+          <t>20-Mar-2024 (Wed)</t>
         </is>
       </c>
       <c r="G30" s="15" t="n">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>02-Apr-2024 (Tue)</t>
+          <t>01-Apr-2024 (Mon)</t>
         </is>
       </c>
       <c r="J30" s="15" t="n">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>07-Mar-2024 (Thu)</t>
+          <t>14-Mar-2024 (Thu)</t>
         </is>
       </c>
       <c r="G31" s="15" t="n">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>20-Mar-2024 (Wed)</t>
+          <t>22-Mar-2024 (Fri)</t>
         </is>
       </c>
       <c r="J31" s="15" t="n">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>21-Feb-2024 (Wed)</t>
+          <t>26-Feb-2024 (Mon)</t>
         </is>
       </c>
       <c r="J32" s="15" t="n">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>11-Jan-2024 (Thu)</t>
+          <t>12-Jan-2024 (Fri)</t>
         </is>
       </c>
       <c r="G33" s="15" t="n">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>24-Jan-2024 (Wed)</t>
+          <t>23-Jan-2024 (Tue)</t>
         </is>
       </c>
       <c r="J33" s="15" t="n">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>21-Feb-2024 (Wed)</t>
+          <t>26-Feb-2024 (Mon)</t>
         </is>
       </c>
       <c r="J34" s="15" t="n">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>05-Mar-2024 (Tue)</t>
+          <t>07-Mar-2024 (Thu)</t>
         </is>
       </c>
       <c r="G35" s="15" t="n">
@@ -11296,7 +11296,7 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>19-Mar-2024 (Tue)</t>
+          <t>18-Mar-2024 (Mon)</t>
         </is>
       </c>
       <c r="J35" s="15" t="n">
@@ -11357,7 +11357,7 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>11-Jan-2024 (Thu)</t>
+          <t>12-Jan-2024 (Fri)</t>
         </is>
       </c>
       <c r="G36" s="15" t="n">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>17-Jan-2024 (Wed)</t>
+          <t>23-Jan-2024 (Tue)</t>
         </is>
       </c>
       <c r="J36" s="15" t="n">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>09-Jan-2024 (Tue)</t>
+          <t>12-Jan-2024 (Fri)</t>
         </is>
       </c>
       <c r="G37" s="15" t="n">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>19-Jan-2024 (Fri)</t>
+          <t>23-Jan-2024 (Tue)</t>
         </is>
       </c>
       <c r="J37" s="15" t="n">
@@ -11579,7 +11579,7 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>12-Jan-2024 (Fri)</t>
+          <t>17-Jan-2024 (Wed)</t>
         </is>
       </c>
       <c r="G39" s="15" t="n">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>24-Jan-2024 (Wed)</t>
+          <t>29-Jan-2024 (Mon)</t>
         </is>
       </c>
       <c r="J39" s="15" t="n">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>07-Mar-2024 (Thu)</t>
+          <t>14-Mar-2024 (Thu)</t>
         </is>
       </c>
       <c r="G40" s="15" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>01-Jan-2024 (Mon)</t>
+          <t>08-Jan-2024 (Mon)</t>
         </is>
       </c>
       <c r="G41" s="15" t="n">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>17-Jan-2024 (Wed)</t>
+          <t>16-Jan-2024 (Tue)</t>
         </is>
       </c>
       <c r="J41" s="15" t="n">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>02-Feb-2024 (Fri)</t>
+          <t>07-Feb-2024 (Wed)</t>
         </is>
       </c>
       <c r="G42" s="15" t="n">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>14-Feb-2024 (Wed)</t>
+          <t>15-Feb-2024 (Thu)</t>
         </is>
       </c>
       <c r="J42" s="15" t="n">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>11-Jan-2024 (Thu)</t>
+          <t>12-Jan-2024 (Fri)</t>
         </is>
       </c>
       <c r="G43" s="15" t="n">
@@ -11888,7 +11888,7 @@
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>24-Jan-2024 (Wed)</t>
+          <t>23-Jan-2024 (Tue)</t>
         </is>
       </c>
       <c r="J43" s="15" t="n">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>05-Mar-2024 (Tue)</t>
+          <t>07-Mar-2024 (Thu)</t>
         </is>
       </c>
       <c r="G44" s="15" t="n">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>19-Mar-2024 (Tue)</t>
+          <t>18-Mar-2024 (Mon)</t>
         </is>
       </c>
       <c r="J44" s="15" t="n">
@@ -12023,7 +12023,7 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>06-Feb-2024 (Tue)</t>
+          <t>07-Feb-2024 (Wed)</t>
         </is>
       </c>
       <c r="G45" s="15" t="n">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>16-Feb-2024 (Fri)</t>
+          <t>15-Feb-2024 (Thu)</t>
         </is>
       </c>
       <c r="J45" s="15" t="n">
@@ -12097,7 +12097,7 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>08-Jan-2024 (Mon)</t>
+          <t>10-Jan-2024 (Wed)</t>
         </is>
       </c>
       <c r="G46" s="15" t="n">
@@ -12110,7 +12110,7 @@
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>17-Jan-2024 (Wed)</t>
+          <t>18-Jan-2024 (Thu)</t>
         </is>
       </c>
       <c r="J46" s="15" t="n">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>09-Feb-2024 (Fri)</t>
+          <t>14-Feb-2024 (Wed)</t>
         </is>
       </c>
       <c r="G47" s="15" t="n">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>20-Feb-2024 (Tue)</t>
+          <t>22-Feb-2024 (Thu)</t>
         </is>
       </c>
       <c r="J47" s="15" t="n">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>02-Feb-2024 (Fri)</t>
+          <t>07-Feb-2024 (Wed)</t>
         </is>
       </c>
       <c r="G49" s="15" t="n">
@@ -12332,7 +12332,7 @@
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>14-Feb-2024 (Wed)</t>
+          <t>15-Feb-2024 (Thu)</t>
         </is>
       </c>
       <c r="J49" s="15" t="n">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>11-Jan-2024 (Thu)</t>
+          <t>17-Jan-2024 (Wed)</t>
         </is>
       </c>
       <c r="G50" s="15" t="n">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>25-Jan-2024 (Thu)</t>
+          <t>29-Jan-2024 (Mon)</t>
         </is>
       </c>
       <c r="J50" s="15" t="n">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>11-Jan-2024 (Thu)</t>
+          <t>12-Jan-2024 (Fri)</t>
         </is>
       </c>
       <c r="G52" s="15" t="n">
@@ -12554,7 +12554,7 @@
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>24-Jan-2024 (Wed)</t>
+          <t>23-Jan-2024 (Tue)</t>
         </is>
       </c>
       <c r="J52" s="15" t="n">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>12-Jan-2024 (Fri)</t>
+          <t>17-Jan-2024 (Wed)</t>
         </is>
       </c>
       <c r="G53" s="15" t="n">
@@ -12628,7 +12628,7 @@
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>24-Jan-2024 (Wed)</t>
+          <t>29-Jan-2024 (Mon)</t>
         </is>
       </c>
       <c r="J53" s="15" t="n">
@@ -12689,7 +12689,7 @@
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>07-Mar-2024 (Thu)</t>
+          <t>13-Mar-2024 (Wed)</t>
         </is>
       </c>
       <c r="G54" s="15" t="n">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>16-Oct-2023 (Mon)</t>
+          <t>19-Oct-2023 (Thu)</t>
         </is>
       </c>
       <c r="J5" s="15" t="n">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>19-Dec-2023 (Tue)</t>
+          <t>18-Dec-2023 (Mon)</t>
         </is>
       </c>
       <c r="J7" s="15" t="n">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>19-Dec-2023 (Tue)</t>
+          <t>22-Dec-2023 (Fri)</t>
         </is>
       </c>
       <c r="J8" s="15" t="n">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>01-Dec-2023 (Fri)</t>
+          <t>08-Dec-2023 (Fri)</t>
         </is>
       </c>
       <c r="G9" s="15" t="n">
@@ -13217,7 +13217,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>14-Dec-2023 (Thu)</t>
+          <t>18-Dec-2023 (Mon)</t>
         </is>
       </c>
       <c r="J9" s="15" t="n">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>10-Nov-2023 (Fri)</t>
+          <t>16-Nov-2023 (Thu)</t>
         </is>
       </c>
       <c r="G10" s="15" t="n">
@@ -13291,7 +13291,7 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>22-Nov-2023 (Wed)</t>
+          <t>24-Nov-2023 (Fri)</t>
         </is>
       </c>
       <c r="J10" s="15" t="n">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>06-Oct-2023 (Fri)</t>
+          <t>11-Oct-2023 (Wed)</t>
         </is>
       </c>
       <c r="G11" s="15" t="n">
@@ -13426,7 +13426,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>07-Dec-2023 (Thu)</t>
+          <t>13-Dec-2023 (Wed)</t>
         </is>
       </c>
       <c r="G12" s="15" t="n">
@@ -13439,7 +13439,7 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>20-Dec-2023 (Wed)</t>
+          <t>21-Dec-2023 (Thu)</t>
         </is>
       </c>
       <c r="J12" s="15" t="n">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>19-Dec-2023 (Tue)</t>
+          <t>20-Dec-2023 (Wed)</t>
         </is>
       </c>
       <c r="G13" s="15" t="n">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>01-Jan-2024 (Mon)</t>
+          <t>29-Dec-2023 (Fri)</t>
         </is>
       </c>
       <c r="J13" s="15" t="n">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>29-Sep-2023 (Fri)</t>
+          <t>06-Oct-2023 (Fri)</t>
         </is>
       </c>
       <c r="G15" s="15" t="n">
@@ -13661,7 +13661,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>13-Oct-2023 (Fri)</t>
+          <t>16-Oct-2023 (Mon)</t>
         </is>
       </c>
       <c r="J15" s="15" t="n">
@@ -13722,7 +13722,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>04-Oct-2023 (Wed)</t>
+          <t>11-Oct-2023 (Wed)</t>
         </is>
       </c>
       <c r="G16" s="15" t="n">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>20-Oct-2023 (Fri)</t>
+          <t>19-Oct-2023 (Thu)</t>
         </is>
       </c>
       <c r="J16" s="15" t="n">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>10-Nov-2023 (Fri)</t>
+          <t>15-Nov-2023 (Wed)</t>
         </is>
       </c>
       <c r="G17" s="15" t="n">
@@ -13809,7 +13809,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>21-Nov-2023 (Tue)</t>
+          <t>23-Nov-2023 (Thu)</t>
         </is>
       </c>
       <c r="J17" s="15" t="n">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>11-Oct-2023 (Wed)</t>
+          <t>18-Oct-2023 (Wed)</t>
         </is>
       </c>
       <c r="G18" s="15" t="n">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>25-Oct-2023 (Wed)</t>
+          <t>27-Oct-2023 (Fri)</t>
         </is>
       </c>
       <c r="J18" s="15" t="n">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>06-Nov-2023 (Mon)</t>
+          <t>08-Nov-2023 (Wed)</t>
         </is>
       </c>
       <c r="G19" s="15" t="n">
@@ -13957,7 +13957,7 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>13-Nov-2023 (Mon)</t>
+          <t>17-Nov-2023 (Fri)</t>
         </is>
       </c>
       <c r="J19" s="15" t="n">
@@ -14092,7 +14092,7 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>09-Nov-2023 (Thu)</t>
+          <t>15-Nov-2023 (Wed)</t>
         </is>
       </c>
       <c r="G21" s="15" t="n">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>24-Nov-2023 (Fri)</t>
+          <t>23-Nov-2023 (Thu)</t>
         </is>
       </c>
       <c r="J21" s="15" t="n">
@@ -14166,7 +14166,7 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>08-Dec-2023 (Fri)</t>
+          <t>13-Dec-2023 (Wed)</t>
         </is>
       </c>
       <c r="G22" s="15" t="n">
@@ -14179,7 +14179,7 @@
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>19-Dec-2023 (Tue)</t>
+          <t>21-Dec-2023 (Thu)</t>
         </is>
       </c>
       <c r="J22" s="15" t="n">
@@ -14240,7 +14240,7 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>08-Nov-2023 (Wed)</t>
+          <t>09-Nov-2023 (Thu)</t>
         </is>
       </c>
       <c r="G23" s="15" t="n">
@@ -14253,7 +14253,7 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>17-Nov-2023 (Fri)</t>
+          <t>20-Nov-2023 (Mon)</t>
         </is>
       </c>
       <c r="J23" s="15" t="n">
@@ -14327,7 +14327,7 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>30-Oct-2023 (Mon)</t>
+          <t>27-Oct-2023 (Fri)</t>
         </is>
       </c>
       <c r="J24" s="15" t="n">
@@ -14388,7 +14388,7 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>16-Nov-2023 (Thu)</t>
+          <t>21-Nov-2023 (Tue)</t>
         </is>
       </c>
       <c r="G25" s="15" t="n">
@@ -14462,7 +14462,7 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>04-Oct-2023 (Wed)</t>
+          <t>06-Oct-2023 (Fri)</t>
         </is>
       </c>
       <c r="G26" s="15" t="n">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>17-Oct-2023 (Tue)</t>
+          <t>16-Oct-2023 (Mon)</t>
         </is>
       </c>
       <c r="J26" s="15" t="n">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>03-Oct-2023 (Tue)</t>
+          <t>06-Oct-2023 (Fri)</t>
         </is>
       </c>
       <c r="G27" s="15" t="n">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>12-Oct-2023 (Thu)</t>
+          <t>16-Oct-2023 (Mon)</t>
         </is>
       </c>
       <c r="J27" s="15" t="n">
@@ -14623,7 +14623,7 @@
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>24-Nov-2023 (Fri)</t>
+          <t>23-Nov-2023 (Thu)</t>
         </is>
       </c>
       <c r="J28" s="15" t="n">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>15-Nov-2023 (Wed)</t>
+          <t>16-Nov-2023 (Thu)</t>
         </is>
       </c>
       <c r="G30" s="15" t="n">
@@ -14771,7 +14771,7 @@
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>22-Nov-2023 (Wed)</t>
+          <t>24-Nov-2023 (Fri)</t>
         </is>
       </c>
       <c r="J30" s="15" t="n">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>06-Dec-2023 (Wed)</t>
+          <t>08-Dec-2023 (Fri)</t>
         </is>
       </c>
       <c r="G32" s="15" t="n">
@@ -14919,7 +14919,7 @@
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>14-Dec-2023 (Thu)</t>
+          <t>18-Dec-2023 (Mon)</t>
         </is>
       </c>
       <c r="J32" s="15" t="n">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>11-Dec-2023 (Mon)</t>
+          <t>14-Dec-2023 (Thu)</t>
         </is>
       </c>
       <c r="G33" s="15" t="n">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>05-Dec-2023 (Tue)</t>
+          <t>08-Dec-2023 (Fri)</t>
         </is>
       </c>
       <c r="G34" s="15" t="n">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>19-Dec-2023 (Tue)</t>
+          <t>18-Dec-2023 (Mon)</t>
         </is>
       </c>
       <c r="J34" s="15" t="n">
@@ -15128,7 +15128,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>05-Dec-2023 (Tue)</t>
+          <t>08-Dec-2023 (Fri)</t>
         </is>
       </c>
       <c r="G35" s="15" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>19-Dec-2023 (Tue)</t>
+          <t>18-Dec-2023 (Mon)</t>
         </is>
       </c>
       <c r="J35" s="15" t="n">
@@ -15202,7 +15202,7 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>11-Dec-2023 (Mon)</t>
+          <t>14-Dec-2023 (Thu)</t>
         </is>
       </c>
       <c r="G36" s="15" t="n">
@@ -15276,7 +15276,7 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>15-Nov-2023 (Wed)</t>
+          <t>16-Nov-2023 (Thu)</t>
         </is>
       </c>
       <c r="G37" s="15" t="n">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>22-Nov-2023 (Wed)</t>
+          <t>24-Nov-2023 (Fri)</t>
         </is>
       </c>
       <c r="J37" s="15" t="n">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>13-Dec-2023 (Wed)</t>
+          <t>19-Dec-2023 (Tue)</t>
         </is>
       </c>
       <c r="G38" s="15" t="n">
@@ -15424,7 +15424,7 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>11-Dec-2023 (Mon)</t>
+          <t>13-Dec-2023 (Wed)</t>
         </is>
       </c>
       <c r="G39" s="15" t="n">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>22-Dec-2023 (Fri)</t>
+          <t>21-Dec-2023 (Thu)</t>
         </is>
       </c>
       <c r="J39" s="15" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>02-Nov-2023 (Thu)</t>
+          <t>08-Nov-2023 (Wed)</t>
         </is>
       </c>
       <c r="G40" s="15" t="n">
@@ -15511,7 +15511,7 @@
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>15-Nov-2023 (Wed)</t>
+          <t>17-Nov-2023 (Fri)</t>
         </is>
       </c>
       <c r="J40" s="15" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>10-Oct-2023 (Tue)</t>
+          <t>12-Oct-2023 (Thu)</t>
         </is>
       </c>
       <c r="G41" s="15" t="n">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>17-Oct-2023 (Tue)</t>
+          <t>20-Oct-2023 (Fri)</t>
         </is>
       </c>
       <c r="J41" s="15" t="n">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>06-Oct-2023 (Fri)</t>
+          <t>12-Oct-2023 (Thu)</t>
         </is>
       </c>
       <c r="G42" s="15" t="n">
@@ -15659,7 +15659,7 @@
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>18-Oct-2023 (Wed)</t>
+          <t>20-Oct-2023 (Fri)</t>
         </is>
       </c>
       <c r="J42" s="15" t="n">
@@ -15720,7 +15720,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>06-Oct-2023 (Fri)</t>
+          <t>11-Oct-2023 (Wed)</t>
         </is>
       </c>
       <c r="G43" s="15" t="n">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>06-Oct-2023 (Fri)</t>
+          <t>12-Oct-2023 (Thu)</t>
         </is>
       </c>
       <c r="G44" s="15" t="n">
@@ -15868,7 +15868,7 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>06-Oct-2023 (Fri)</t>
+          <t>12-Oct-2023 (Thu)</t>
         </is>
       </c>
       <c r="G45" s="15" t="n">
@@ -15881,7 +15881,7 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>18-Oct-2023 (Wed)</t>
+          <t>20-Oct-2023 (Fri)</t>
         </is>
       </c>
       <c r="J45" s="15" t="n">
@@ -15942,7 +15942,7 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>12-Dec-2023 (Tue)</t>
+          <t>13-Dec-2023 (Wed)</t>
         </is>
       </c>
       <c r="G46" s="15" t="n">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>19-Dec-2023 (Tue)</t>
+          <t>21-Dec-2023 (Thu)</t>
         </is>
       </c>
       <c r="J46" s="15" t="n">
@@ -16090,7 +16090,7 @@
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>06-Oct-2023 (Fri)</t>
+          <t>12-Oct-2023 (Thu)</t>
         </is>
       </c>
       <c r="G48" s="15" t="n">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>18-Oct-2023 (Wed)</t>
+          <t>20-Oct-2023 (Fri)</t>
         </is>
       </c>
       <c r="J48" s="15" t="n">
@@ -16177,7 +16177,7 @@
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>30-Oct-2023 (Mon)</t>
+          <t>27-Oct-2023 (Fri)</t>
         </is>
       </c>
       <c r="J49" s="15" t="n">
@@ -16238,7 +16238,7 @@
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>02-Nov-2023 (Thu)</t>
+          <t>08-Nov-2023 (Wed)</t>
         </is>
       </c>
       <c r="G50" s="15" t="n">
@@ -16312,7 +16312,7 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>07-Dec-2023 (Thu)</t>
+          <t>14-Dec-2023 (Thu)</t>
         </is>
       </c>
       <c r="G51" s="15" t="n">
@@ -16325,7 +16325,7 @@
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>26-Dec-2023 (Tue)</t>
+          <t>22-Dec-2023 (Fri)</t>
         </is>
       </c>
       <c r="J51" s="15" t="n">
@@ -16399,7 +16399,7 @@
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>30-Oct-2023 (Mon)</t>
+          <t>27-Oct-2023 (Fri)</t>
         </is>
       </c>
       <c r="J52" s="15" t="n">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>07-Dec-2023 (Thu)</t>
+          <t>13-Dec-2023 (Wed)</t>
         </is>
       </c>
       <c r="G54" s="15" t="n">
@@ -16547,7 +16547,7 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>20-Dec-2023 (Wed)</t>
+          <t>21-Dec-2023 (Thu)</t>
         </is>
       </c>
       <c r="J54" s="15" t="n">
@@ -16827,7 +16827,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>17-Jul-2026 (Fri)</t>
+          <t>23-Jul-2026 (Thu)</t>
         </is>
       </c>
       <c r="G6" s="15" t="n">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>29-Jul-2026 (Wed)</t>
+          <t>31-Jul-2026 (Fri)</t>
         </is>
       </c>
       <c r="J6" s="15" t="n">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>16-Jul-2026 (Thu)</t>
+          <t>23-Jul-2026 (Thu)</t>
         </is>
       </c>
       <c r="G7" s="15" t="n">
@@ -16914,7 +16914,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>03-Aug-2026 (Mon)</t>
+          <t>31-Jul-2026 (Fri)</t>
         </is>
       </c>
       <c r="J7" s="15" t="n">
@@ -16975,7 +16975,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>13-Jul-2026 (Mon)</t>
+          <t>14-Jul-2026 (Tue)</t>
         </is>
       </c>
       <c r="G8" s="15" t="n">
@@ -16988,7 +16988,7 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>23-Jul-2026 (Thu)</t>
+          <t>22-Jul-2026 (Wed)</t>
         </is>
       </c>
       <c r="J8" s="15" t="n">
@@ -17062,7 +17062,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>03-Aug-2026 (Mon)</t>
+          <t>06-Aug-2026 (Thu)</t>
         </is>
       </c>
       <c r="J9" s="15" t="n">
@@ -17123,7 +17123,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>31-Jul-2026 (Fri)</t>
+          <t>03-Aug-2026 (Mon)</t>
         </is>
       </c>
       <c r="G10" s="15" t="n">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>07-Aug-2026 (Fri)</t>
+          <t>11-Aug-2026 (Tue)</t>
         </is>
       </c>
       <c r="J10" s="15" t="n">
@@ -17197,7 +17197,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>29-Jul-2026 (Wed)</t>
+          <t>31-Jul-2026 (Fri)</t>
         </is>
       </c>
       <c r="G11" s="15" t="n">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>11-Aug-2026 (Tue)</t>
+          <t>10-Aug-2026 (Mon)</t>
         </is>
       </c>
       <c r="J11" s="15" t="n">
@@ -17271,7 +17271,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>03-Aug-2026 (Mon)</t>
+          <t>05-Aug-2026 (Wed)</t>
         </is>
       </c>
       <c r="G12" s="15" t="n">
@@ -17284,7 +17284,7 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>10-Aug-2026 (Mon)</t>
+          <t>13-Aug-2026 (Thu)</t>
         </is>
       </c>
       <c r="J12" s="15" t="n">
@@ -17345,7 +17345,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>22-Jul-2026 (Wed)</t>
+          <t>28-Jul-2026 (Tue)</t>
         </is>
       </c>
       <c r="G13" s="15" t="n">
@@ -17358,7 +17358,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>03-Aug-2026 (Mon)</t>
+          <t>05-Aug-2026 (Wed)</t>
         </is>
       </c>
       <c r="J13" s="15" t="n">
@@ -17419,7 +17419,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>03-Aug-2026 (Mon)</t>
+          <t>05-Aug-2026 (Wed)</t>
         </is>
       </c>
       <c r="G14" s="15" t="n">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>12-Aug-2026 (Wed)</t>
+          <t>13-Aug-2026 (Thu)</t>
         </is>
       </c>
       <c r="J14" s="15" t="n">
@@ -17506,7 +17506,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>20-Jul-2026 (Mon)</t>
+          <t>23-Jul-2026 (Thu)</t>
         </is>
       </c>
       <c r="J15" s="15" t="n">
@@ -17567,7 +17567,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>21-Jul-2026 (Tue)</t>
+          <t>22-Jul-2026 (Wed)</t>
         </is>
       </c>
       <c r="G16" s="15" t="n">
@@ -17580,7 +17580,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>28-Jul-2026 (Tue)</t>
+          <t>30-Jul-2026 (Thu)</t>
         </is>
       </c>
       <c r="J16" s="15" t="n">
@@ -17641,7 +17641,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>27-Jul-2026 (Mon)</t>
+          <t>29-Jul-2026 (Wed)</t>
         </is>
       </c>
       <c r="G17" s="15" t="n">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>04-Aug-2026 (Tue)</t>
+          <t>06-Aug-2026 (Thu)</t>
         </is>
       </c>
       <c r="J17" s="15" t="n">
@@ -17715,7 +17715,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>15-Jul-2026 (Wed)</t>
+          <t>22-Jul-2026 (Wed)</t>
         </is>
       </c>
       <c r="G18" s="15" t="n">
@@ -17728,7 +17728,7 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>31-Jul-2026 (Fri)</t>
+          <t>30-Jul-2026 (Thu)</t>
         </is>
       </c>
       <c r="J18" s="15" t="n">
@@ -17789,7 +17789,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>15-Jul-2026 (Wed)</t>
+          <t>21-Jul-2026 (Tue)</t>
         </is>
       </c>
       <c r="G19" s="15" t="n">
@@ -17863,7 +17863,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>16-Jul-2026 (Thu)</t>
+          <t>22-Jul-2026 (Wed)</t>
         </is>
       </c>
       <c r="G20" s="15" t="n">
@@ -17876,7 +17876,7 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>29-Jul-2026 (Wed)</t>
+          <t>30-Jul-2026 (Thu)</t>
         </is>
       </c>
       <c r="J20" s="15" t="n">
@@ -17937,7 +17937,7 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>06-Jul-2026 (Mon)</t>
+          <t>13-Jul-2026 (Mon)</t>
         </is>
       </c>
       <c r="G21" s="15" t="n">
@@ -17950,7 +17950,7 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>17-Jul-2026 (Fri)</t>
+          <t>21-Jul-2026 (Tue)</t>
         </is>
       </c>
       <c r="J21" s="15" t="n">
@@ -18011,7 +18011,7 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>09-Jul-2026 (Thu)</t>
+          <t>15-Jul-2026 (Wed)</t>
         </is>
       </c>
       <c r="G22" s="15" t="n">
@@ -18085,7 +18085,7 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>09-Jul-2026 (Thu)</t>
+          <t>15-Jul-2026 (Wed)</t>
         </is>
       </c>
       <c r="G23" s="15" t="n">
@@ -18098,7 +18098,7 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>22-Jul-2026 (Wed)</t>
+          <t>23-Jul-2026 (Thu)</t>
         </is>
       </c>
       <c r="J23" s="15" t="n">
@@ -18159,7 +18159,7 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>28-Jul-2026 (Tue)</t>
+          <t>31-Jul-2026 (Fri)</t>
         </is>
       </c>
       <c r="G24" s="15" t="n">
@@ -18172,7 +18172,7 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>06-Aug-2026 (Thu)</t>
+          <t>10-Aug-2026 (Mon)</t>
         </is>
       </c>
       <c r="J24" s="15" t="n">
@@ -18307,7 +18307,7 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>23-Jul-2026 (Thu)</t>
+          <t>27-Jul-2026 (Mon)</t>
         </is>
       </c>
       <c r="G26" s="15" t="n">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>05-Aug-2026 (Wed)</t>
+          <t>04-Aug-2026 (Tue)</t>
         </is>
       </c>
       <c r="J26" s="15" t="n">
@@ -18455,7 +18455,7 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>17-Jul-2026 (Fri)</t>
+          <t>20-Jul-2026 (Mon)</t>
         </is>
       </c>
       <c r="G28" s="15" t="n">
@@ -18468,7 +18468,7 @@
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>23-Jul-2026 (Thu)</t>
+          <t>28-Jul-2026 (Tue)</t>
         </is>
       </c>
       <c r="J28" s="15" t="n">
@@ -18529,7 +18529,7 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>16-Jul-2026 (Thu)</t>
+          <t>21-Jul-2026 (Tue)</t>
         </is>
       </c>
       <c r="G29" s="15" t="n">
@@ -18677,7 +18677,7 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>21-Jul-2026 (Tue)</t>
+          <t>27-Jul-2026 (Mon)</t>
         </is>
       </c>
       <c r="G31" s="15" t="n">
@@ -18825,7 +18825,7 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>07-Jul-2026 (Tue)</t>
+          <t>09-Jul-2026 (Thu)</t>
         </is>
       </c>
       <c r="G33" s="15" t="n">
@@ -18838,7 +18838,7 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>16-Jul-2026 (Thu)</t>
+          <t>17-Jul-2026 (Fri)</t>
         </is>
       </c>
       <c r="J33" s="15" t="n">
@@ -18973,7 +18973,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>21-Jul-2026 (Tue)</t>
+          <t>22-Jul-2026 (Wed)</t>
         </is>
       </c>
       <c r="G35" s="15" t="n">
@@ -18986,7 +18986,7 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>29-Jul-2026 (Wed)</t>
+          <t>30-Jul-2026 (Thu)</t>
         </is>
       </c>
       <c r="J35" s="15" t="n">
@@ -19121,7 +19121,7 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>09-Jul-2026 (Thu)</t>
+          <t>15-Jul-2026 (Wed)</t>
         </is>
       </c>
       <c r="G37" s="15" t="n">
@@ -19269,7 +19269,7 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>09-Jul-2026 (Thu)</t>
+          <t>14-Jul-2026 (Tue)</t>
         </is>
       </c>
       <c r="G39" s="15" t="n">
@@ -19282,7 +19282,7 @@
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>20-Jul-2026 (Mon)</t>
+          <t>22-Jul-2026 (Wed)</t>
         </is>
       </c>
       <c r="J39" s="15" t="n">
@@ -19356,7 +19356,7 @@
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>31-Jul-2026 (Fri)</t>
+          <t>05-Aug-2026 (Wed)</t>
         </is>
       </c>
       <c r="J40" s="15" t="n">
@@ -19417,7 +19417,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>17-Jul-2026 (Fri)</t>
+          <t>20-Jul-2026 (Mon)</t>
         </is>
       </c>
       <c r="G41" s="15" t="n">
@@ -19430,7 +19430,7 @@
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>23-Jul-2026 (Thu)</t>
+          <t>28-Jul-2026 (Tue)</t>
         </is>
       </c>
       <c r="J41" s="15" t="n">
@@ -19565,7 +19565,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>28-Jul-2026 (Tue)</t>
+          <t>29-Jul-2026 (Wed)</t>
         </is>
       </c>
       <c r="G43" s="15" t="n">
@@ -19578,7 +19578,7 @@
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>04-Aug-2026 (Tue)</t>
+          <t>06-Aug-2026 (Thu)</t>
         </is>
       </c>
       <c r="J43" s="15" t="n">
@@ -19639,7 +19639,7 @@
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>22-Jul-2026 (Wed)</t>
+          <t>27-Jul-2026 (Mon)</t>
         </is>
       </c>
       <c r="G44" s="15" t="n">
@@ -19713,7 +19713,7 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>15-Jul-2026 (Wed)</t>
+          <t>16-Jul-2026 (Thu)</t>
         </is>
       </c>
       <c r="G45" s="15" t="n">
@@ -19726,7 +19726,7 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>21-Jul-2026 (Tue)</t>
+          <t>24-Jul-2026 (Fri)</t>
         </is>
       </c>
       <c r="J45" s="15" t="n">
@@ -19787,7 +19787,7 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>04-Aug-2026 (Tue)</t>
+          <t>05-Aug-2026 (Wed)</t>
         </is>
       </c>
       <c r="G46" s="15" t="n">
@@ -19800,7 +19800,7 @@
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>12-Aug-2026 (Wed)</t>
+          <t>13-Aug-2026 (Thu)</t>
         </is>
       </c>
       <c r="J46" s="15" t="n">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>20-Jul-2026 (Mon)</t>
+          <t>24-Jul-2026 (Fri)</t>
         </is>
       </c>
       <c r="G47" s="15" t="n">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>31-Jul-2026 (Fri)</t>
+          <t>03-Aug-2026 (Mon)</t>
         </is>
       </c>
       <c r="J47" s="15" t="n">
@@ -19935,7 +19935,7 @@
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>14-Jul-2026 (Tue)</t>
+          <t>15-Jul-2026 (Wed)</t>
         </is>
       </c>
       <c r="G48" s="15" t="n">
@@ -19948,7 +19948,7 @@
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>24-Jul-2026 (Fri)</t>
+          <t>23-Jul-2026 (Thu)</t>
         </is>
       </c>
       <c r="J48" s="15" t="n">
@@ -20009,7 +20009,7 @@
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>23-Jul-2026 (Thu)</t>
+          <t>24-Jul-2026 (Fri)</t>
         </is>
       </c>
       <c r="G49" s="15" t="n">
@@ -20022,7 +20022,7 @@
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>30-Jul-2026 (Thu)</t>
+          <t>03-Aug-2026 (Mon)</t>
         </is>
       </c>
       <c r="J49" s="15" t="n">
@@ -20083,7 +20083,7 @@
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>07-Aug-2026 (Fri)</t>
+          <t>10-Aug-2026 (Mon)</t>
         </is>
       </c>
       <c r="G50" s="15" t="n">
@@ -20096,7 +20096,7 @@
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>17-Aug-2026 (Mon)</t>
+          <t>18-Aug-2026 (Tue)</t>
         </is>
       </c>
       <c r="J50" s="15" t="n">
@@ -20157,7 +20157,7 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>23-Jul-2026 (Thu)</t>
+          <t>27-Jul-2026 (Mon)</t>
         </is>
       </c>
       <c r="G51" s="15" t="n">
@@ -20170,7 +20170,7 @@
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>30-Jul-2026 (Thu)</t>
+          <t>04-Aug-2026 (Tue)</t>
         </is>
       </c>
       <c r="J51" s="15" t="n">
@@ -20231,7 +20231,7 @@
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>22-Jul-2026 (Wed)</t>
+          <t>29-Jul-2026 (Wed)</t>
         </is>
       </c>
       <c r="G52" s="15" t="n">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>07-Aug-2026 (Fri)</t>
+          <t>06-Aug-2026 (Thu)</t>
         </is>
       </c>
       <c r="J52" s="15" t="n">
@@ -20305,7 +20305,7 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>16-Jul-2026 (Thu)</t>
+          <t>17-Jul-2026 (Fri)</t>
         </is>
       </c>
       <c r="G53" s="15" t="n">
@@ -20318,7 +20318,7 @@
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>23-Jul-2026 (Thu)</t>
+          <t>27-Jul-2026 (Mon)</t>
         </is>
       </c>
       <c r="J53" s="15" t="n">
@@ -20379,7 +20379,7 @@
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>22-Jul-2026 (Wed)</t>
+          <t>28-Jul-2026 (Tue)</t>
         </is>
       </c>
       <c r="G54" s="15" t="n">
@@ -20746,7 +20746,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>05-Jun-2026 (Fri)</t>
+          <t>10-Jun-2026 (Wed)</t>
         </is>
       </c>
       <c r="G7" s="15" t="n">
@@ -20759,7 +20759,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>19-Jun-2026 (Fri)</t>
+          <t>18-Jun-2026 (Thu)</t>
         </is>
       </c>
       <c r="J7" s="15" t="n">
@@ -20820,7 +20820,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>08-Jun-2026 (Mon)</t>
+          <t>10-Jun-2026 (Wed)</t>
         </is>
       </c>
       <c r="G8" s="15" t="n">
@@ -20833,7 +20833,7 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>16-Jun-2026 (Tue)</t>
+          <t>18-Jun-2026 (Thu)</t>
         </is>
       </c>
       <c r="J8" s="15" t="n">
@@ -20894,7 +20894,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>16-Apr-2026 (Thu)</t>
+          <t>20-Apr-2026 (Mon)</t>
         </is>
       </c>
       <c r="G9" s="15" t="n">
@@ -20907,7 +20907,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>24-Apr-2026 (Fri)</t>
+          <t>28-Apr-2026 (Tue)</t>
         </is>
       </c>
       <c r="J9" s="15" t="n">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>06-Apr-2026 (Mon)</t>
+          <t>08-Apr-2026 (Wed)</t>
         </is>
       </c>
       <c r="G10" s="15" t="n">
@@ -20981,7 +20981,7 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>20-Apr-2026 (Mon)</t>
+          <t>17-Apr-2026 (Fri)</t>
         </is>
       </c>
       <c r="J10" s="15" t="n">
@@ -21042,7 +21042,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>15-May-2026 (Fri)</t>
+          <t>18-May-2026 (Mon)</t>
         </is>
       </c>
       <c r="G11" s="15" t="n">
@@ -21055,7 +21055,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>22-May-2026 (Fri)</t>
+          <t>26-May-2026 (Tue)</t>
         </is>
       </c>
       <c r="J11" s="15" t="n">
@@ -21190,7 +21190,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>19-Jun-2026 (Fri)</t>
+          <t>22-Jun-2026 (Mon)</t>
         </is>
       </c>
       <c r="G13" s="15" t="n">
@@ -21203,7 +21203,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>25-Jun-2026 (Thu)</t>
+          <t>30-Jun-2026 (Tue)</t>
         </is>
       </c>
       <c r="J13" s="15" t="n">
@@ -21264,7 +21264,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>06-May-2026 (Wed)</t>
+          <t>13-May-2026 (Wed)</t>
         </is>
       </c>
       <c r="G14" s="15" t="n">
@@ -21277,7 +21277,7 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>19-May-2026 (Tue)</t>
+          <t>21-May-2026 (Thu)</t>
         </is>
       </c>
       <c r="J14" s="15" t="n">
@@ -21338,7 +21338,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>10-Jun-2026 (Wed)</t>
+          <t>11-Jun-2026 (Thu)</t>
         </is>
       </c>
       <c r="G15" s="15" t="n">
@@ -21351,7 +21351,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>17-Jun-2026 (Wed)</t>
+          <t>19-Jun-2026 (Fri)</t>
         </is>
       </c>
       <c r="J15" s="15" t="n">
@@ -21412,7 +21412,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>09-Jun-2026 (Tue)</t>
+          <t>16-Jun-2026 (Tue)</t>
         </is>
       </c>
       <c r="G16" s="15" t="n">
@@ -21425,7 +21425,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>25-Jun-2026 (Thu)</t>
+          <t>24-Jun-2026 (Wed)</t>
         </is>
       </c>
       <c r="J16" s="15" t="n">
@@ -21486,7 +21486,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>30-Apr-2026 (Thu)</t>
+          <t>07-May-2026 (Thu)</t>
         </is>
       </c>
       <c r="G17" s="15" t="n">
@@ -21499,7 +21499,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>13-May-2026 (Wed)</t>
+          <t>15-May-2026 (Fri)</t>
         </is>
       </c>
       <c r="J17" s="15" t="n">
@@ -21560,7 +21560,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>01-Apr-2026 (Wed)</t>
+          <t>09-Apr-2026 (Thu)</t>
         </is>
       </c>
       <c r="G18" s="15" t="n">
@@ -21573,7 +21573,7 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>21-Apr-2026 (Tue)</t>
+          <t>20-Apr-2026 (Mon)</t>
         </is>
       </c>
       <c r="J18" s="15" t="n">
@@ -21634,7 +21634,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>03-Jun-2026 (Wed)</t>
+          <t>10-Jun-2026 (Wed)</t>
         </is>
       </c>
       <c r="G19" s="15" t="n">
@@ -21647,7 +21647,7 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>16-Jun-2026 (Tue)</t>
+          <t>18-Jun-2026 (Thu)</t>
         </is>
       </c>
       <c r="J19" s="15" t="n">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>09-Jun-2026 (Tue)</t>
+          <t>16-Jun-2026 (Tue)</t>
         </is>
       </c>
       <c r="G22" s="15" t="n">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>25-Jun-2026 (Thu)</t>
+          <t>24-Jun-2026 (Wed)</t>
         </is>
       </c>
       <c r="J22" s="15" t="n">
@@ -21930,7 +21930,7 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>15-Jun-2026 (Mon)</t>
+          <t>17-Jun-2026 (Wed)</t>
         </is>
       </c>
       <c r="G23" s="15" t="n">
@@ -21943,7 +21943,7 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>24-Jun-2026 (Wed)</t>
+          <t>25-Jun-2026 (Thu)</t>
         </is>
       </c>
       <c r="J23" s="15" t="n">
@@ -22004,7 +22004,7 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>06-Apr-2026 (Mon)</t>
+          <t>09-Apr-2026 (Thu)</t>
         </is>
       </c>
       <c r="G24" s="15" t="n">
@@ -22091,7 +22091,7 @@
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>25-May-2026 (Mon)</t>
+          <t>28-May-2026 (Thu)</t>
         </is>
       </c>
       <c r="J25" s="15" t="n">
@@ -22152,7 +22152,7 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>16-Apr-2026 (Thu)</t>
+          <t>20-Apr-2026 (Mon)</t>
         </is>
       </c>
       <c r="G26" s="15" t="n">
@@ -22165,7 +22165,7 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>24-Apr-2026 (Fri)</t>
+          <t>28-Apr-2026 (Tue)</t>
         </is>
       </c>
       <c r="J26" s="15" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>08-Jun-2026 (Mon)</t>
+          <t>11-Jun-2026 (Thu)</t>
         </is>
       </c>
       <c r="G27" s="15" t="n">
@@ -22239,7 +22239,7 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>17-Jun-2026 (Wed)</t>
+          <t>19-Jun-2026 (Fri)</t>
         </is>
       </c>
       <c r="J27" s="15" t="n">
@@ -22300,7 +22300,7 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>09-Jun-2026 (Tue)</t>
+          <t>11-Jun-2026 (Thu)</t>
         </is>
       </c>
       <c r="G28" s="15" t="n">
@@ -22313,7 +22313,7 @@
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>22-Jun-2026 (Mon)</t>
+          <t>19-Jun-2026 (Fri)</t>
         </is>
       </c>
       <c r="J28" s="15" t="n">
@@ -22448,7 +22448,7 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>05-Jun-2026 (Fri)</t>
+          <t>11-Jun-2026 (Thu)</t>
         </is>
       </c>
       <c r="G30" s="15" t="n">
@@ -22461,7 +22461,7 @@
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>18-Jun-2026 (Thu)</t>
+          <t>19-Jun-2026 (Fri)</t>
         </is>
       </c>
       <c r="J30" s="15" t="n">
@@ -22522,7 +22522,7 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>05-May-2026 (Tue)</t>
+          <t>07-May-2026 (Thu)</t>
         </is>
       </c>
       <c r="G31" s="15" t="n">
@@ -22535,7 +22535,7 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>14-May-2026 (Thu)</t>
+          <t>15-May-2026 (Fri)</t>
         </is>
       </c>
       <c r="J31" s="15" t="n">
@@ -22596,7 +22596,7 @@
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>07-May-2026 (Thu)</t>
+          <t>12-May-2026 (Tue)</t>
         </is>
       </c>
       <c r="G32" s="15" t="n">
@@ -22609,7 +22609,7 @@
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>19-May-2026 (Tue)</t>
+          <t>20-May-2026 (Wed)</t>
         </is>
       </c>
       <c r="J32" s="15" t="n">
@@ -22670,7 +22670,7 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>09-Apr-2026 (Thu)</t>
+          <t>13-Apr-2026 (Mon)</t>
         </is>
       </c>
       <c r="G33" s="15" t="n">
@@ -22683,7 +22683,7 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>17-Apr-2026 (Fri)</t>
+          <t>22-Apr-2026 (Wed)</t>
         </is>
       </c>
       <c r="J33" s="15" t="n">
@@ -22744,7 +22744,7 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>07-Apr-2026 (Tue)</t>
+          <t>08-Apr-2026 (Wed)</t>
         </is>
       </c>
       <c r="G34" s="15" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>15-Apr-2026 (Wed)</t>
+          <t>17-Apr-2026 (Fri)</t>
         </is>
       </c>
       <c r="J34" s="15" t="n">
@@ -22818,7 +22818,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>11-Jun-2026 (Thu)</t>
+          <t>16-Jun-2026 (Tue)</t>
         </is>
       </c>
       <c r="G35" s="15" t="n">
@@ -22892,7 +22892,7 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>03-Jun-2026 (Wed)</t>
+          <t>10-Jun-2026 (Wed)</t>
         </is>
       </c>
       <c r="G36" s="15" t="n">
@@ -22905,7 +22905,7 @@
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>16-Jun-2026 (Tue)</t>
+          <t>18-Jun-2026 (Thu)</t>
         </is>
       </c>
       <c r="J36" s="15" t="n">
@@ -22966,7 +22966,7 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>01-Apr-2026 (Wed)</t>
+          <t>08-Apr-2026 (Wed)</t>
         </is>
       </c>
       <c r="G37" s="15" t="n">
@@ -22979,7 +22979,7 @@
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>16-Apr-2026 (Thu)</t>
+          <t>17-Apr-2026 (Fri)</t>
         </is>
       </c>
       <c r="J37" s="15" t="n">
@@ -23040,7 +23040,7 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>15-Apr-2026 (Wed)</t>
+          <t>20-Apr-2026 (Mon)</t>
         </is>
       </c>
       <c r="G38" s="15" t="n">
@@ -23053,7 +23053,7 @@
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>29-Apr-2026 (Wed)</t>
+          <t>28-Apr-2026 (Tue)</t>
         </is>
       </c>
       <c r="J38" s="15" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>13-May-2026 (Wed)</t>
+          <t>20-May-2026 (Wed)</t>
         </is>
       </c>
       <c r="G39" s="15" t="n">
@@ -23127,7 +23127,7 @@
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>01-Jun-2026 (Mon)</t>
+          <t>28-May-2026 (Thu)</t>
         </is>
       </c>
       <c r="J39" s="15" t="n">
@@ -23188,7 +23188,7 @@
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>05-May-2026 (Tue)</t>
+          <t>07-May-2026 (Thu)</t>
         </is>
       </c>
       <c r="G40" s="15" t="n">
@@ -23201,7 +23201,7 @@
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>12-May-2026 (Tue)</t>
+          <t>15-May-2026 (Fri)</t>
         </is>
       </c>
       <c r="J40" s="15" t="n">
@@ -23262,7 +23262,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>13-May-2026 (Wed)</t>
+          <t>18-May-2026 (Mon)</t>
         </is>
       </c>
       <c r="G41" s="15" t="n">
@@ -23275,7 +23275,7 @@
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>22-May-2026 (Fri)</t>
+          <t>26-May-2026 (Tue)</t>
         </is>
       </c>
       <c r="J41" s="15" t="n">
@@ -23336,7 +23336,7 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>07-Apr-2026 (Tue)</t>
+          <t>13-Apr-2026 (Mon)</t>
         </is>
       </c>
       <c r="G42" s="15" t="n">
@@ -23349,7 +23349,7 @@
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>20-Apr-2026 (Mon)</t>
+          <t>22-Apr-2026 (Wed)</t>
         </is>
       </c>
       <c r="J42" s="15" t="n">
@@ -23410,7 +23410,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>05-May-2026 (Tue)</t>
+          <t>07-May-2026 (Thu)</t>
         </is>
       </c>
       <c r="G43" s="15" t="n">
@@ -23423,7 +23423,7 @@
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>14-May-2026 (Thu)</t>
+          <t>15-May-2026 (Fri)</t>
         </is>
       </c>
       <c r="J43" s="15" t="n">
@@ -23497,7 +23497,7 @@
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>19-Jun-2026 (Fri)</t>
+          <t>18-Jun-2026 (Thu)</t>
         </is>
       </c>
       <c r="J44" s="15" t="n">
@@ -23558,7 +23558,7 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>11-May-2026 (Mon)</t>
+          <t>13-May-2026 (Wed)</t>
         </is>
       </c>
       <c r="G45" s="15" t="n">
@@ -23571,7 +23571,7 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>19-May-2026 (Tue)</t>
+          <t>21-May-2026 (Thu)</t>
         </is>
       </c>
       <c r="J45" s="15" t="n">
@@ -23632,7 +23632,7 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>09-Apr-2026 (Thu)</t>
+          <t>13-Apr-2026 (Mon)</t>
         </is>
       </c>
       <c r="G46" s="15" t="n">
@@ -23645,7 +23645,7 @@
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>17-Apr-2026 (Fri)</t>
+          <t>22-Apr-2026 (Wed)</t>
         </is>
       </c>
       <c r="J46" s="15" t="n">
@@ -23719,7 +23719,7 @@
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>22-May-2026 (Fri)</t>
+          <t>21-May-2026 (Thu)</t>
         </is>
       </c>
       <c r="J47" s="15" t="n">
@@ -23867,7 +23867,7 @@
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>19-Jun-2026 (Fri)</t>
+          <t>24-Jun-2026 (Wed)</t>
         </is>
       </c>
       <c r="J49" s="15" t="n">
@@ -24002,7 +24002,7 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>13-May-2026 (Wed)</t>
+          <t>18-May-2026 (Mon)</t>
         </is>
       </c>
       <c r="G51" s="15" t="n">
@@ -24015,7 +24015,7 @@
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>22-May-2026 (Fri)</t>
+          <t>26-May-2026 (Tue)</t>
         </is>
       </c>
       <c r="J51" s="15" t="n">
@@ -24076,7 +24076,7 @@
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>01-Apr-2026 (Wed)</t>
+          <t>09-Apr-2026 (Thu)</t>
         </is>
       </c>
       <c r="G52" s="15" t="n">
@@ -24089,7 +24089,7 @@
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>21-Apr-2026 (Tue)</t>
+          <t>20-Apr-2026 (Mon)</t>
         </is>
       </c>
       <c r="J52" s="15" t="n">
@@ -24150,7 +24150,7 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>09-Jun-2026 (Tue)</t>
+          <t>11-Jun-2026 (Thu)</t>
         </is>
       </c>
       <c r="G53" s="15" t="n">
@@ -24163,7 +24163,7 @@
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>22-Jun-2026 (Mon)</t>
+          <t>19-Jun-2026 (Fri)</t>
         </is>
       </c>
       <c r="J53" s="15" t="n">
@@ -24224,7 +24224,7 @@
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>16-Apr-2026 (Thu)</t>
+          <t>20-Apr-2026 (Mon)</t>
         </is>
       </c>
       <c r="G54" s="15" t="n">
@@ -24237,7 +24237,7 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>24-Apr-2026 (Fri)</t>
+          <t>28-Apr-2026 (Tue)</t>
         </is>
       </c>
       <c r="J54" s="15" t="n">
@@ -24443,7 +24443,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>06-Jan-2026 (Tue)</t>
+          <t>09-Jan-2026 (Fri)</t>
         </is>
       </c>
       <c r="G5" s="15" t="n">
@@ -24456,7 +24456,7 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>15-Jan-2026 (Thu)</t>
+          <t>19-Jan-2026 (Mon)</t>
         </is>
       </c>
       <c r="J5" s="15" t="n">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>09-Mar-2026 (Mon)</t>
+          <t>10-Mar-2026 (Tue)</t>
         </is>
       </c>
       <c r="G6" s="15" t="n">
@@ -24530,7 +24530,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>19-Mar-2026 (Thu)</t>
+          <t>18-Mar-2026 (Wed)</t>
         </is>
       </c>
       <c r="J6" s="15" t="n">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>05-Mar-2026 (Thu)</t>
+          <t>10-Mar-2026 (Tue)</t>
         </is>
       </c>
       <c r="G7" s="15" t="n">
@@ -24604,7 +24604,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>17-Mar-2026 (Tue)</t>
+          <t>18-Mar-2026 (Wed)</t>
         </is>
       </c>
       <c r="J7" s="15" t="n">
@@ -24665,7 +24665,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>11-Mar-2026 (Wed)</t>
+          <t>16-Mar-2026 (Mon)</t>
         </is>
       </c>
       <c r="G8" s="15" t="n">
@@ -24678,7 +24678,7 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>23-Mar-2026 (Mon)</t>
+          <t>24-Mar-2026 (Tue)</t>
         </is>
       </c>
       <c r="J8" s="15" t="n">
@@ -24739,7 +24739,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>02-Jan-2026 (Fri)</t>
+          <t>07-Jan-2026 (Wed)</t>
         </is>
       </c>
       <c r="G9" s="15" t="n">
@@ -24752,7 +24752,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>16-Jan-2026 (Fri)</t>
+          <t>15-Jan-2026 (Thu)</t>
         </is>
       </c>
       <c r="J9" s="15" t="n">
@@ -24813,7 +24813,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>18-Feb-2026 (Wed)</t>
+          <t>19-Feb-2026 (Thu)</t>
         </is>
       </c>
       <c r="G10" s="15" t="n">
@@ -24826,7 +24826,7 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>25-Feb-2026 (Wed)</t>
+          <t>27-Feb-2026 (Fri)</t>
         </is>
       </c>
       <c r="J10" s="15" t="n">
@@ -24961,7 +24961,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>15-Jan-2026 (Thu)</t>
+          <t>20-Jan-2026 (Tue)</t>
         </is>
       </c>
       <c r="G12" s="15" t="n">
@@ -24974,7 +24974,7 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>28-Jan-2026 (Wed)</t>
+          <t>29-Jan-2026 (Thu)</t>
         </is>
       </c>
       <c r="J12" s="15" t="n">
@@ -25109,7 +25109,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>07-Jan-2026 (Wed)</t>
+          <t>09-Jan-2026 (Fri)</t>
         </is>
       </c>
       <c r="G14" s="15" t="n">
@@ -25122,7 +25122,7 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>20-Jan-2026 (Tue)</t>
+          <t>19-Jan-2026 (Mon)</t>
         </is>
       </c>
       <c r="J14" s="15" t="n">
@@ -25257,7 +25257,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>12-Mar-2026 (Thu)</t>
+          <t>16-Mar-2026 (Mon)</t>
         </is>
       </c>
       <c r="G16" s="15" t="n">
@@ -25270,7 +25270,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>26-Mar-2026 (Thu)</t>
+          <t>24-Mar-2026 (Tue)</t>
         </is>
       </c>
       <c r="J16" s="15" t="n">
@@ -25331,7 +25331,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>17-Mar-2026 (Tue)</t>
+          <t>20-Mar-2026 (Fri)</t>
         </is>
       </c>
       <c r="G17" s="15" t="n">
@@ -25344,7 +25344,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>25-Mar-2026 (Wed)</t>
+          <t>31-Mar-2026 (Tue)</t>
         </is>
       </c>
       <c r="J17" s="15" t="n">
@@ -25405,7 +25405,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>09-Mar-2026 (Mon)</t>
+          <t>11-Mar-2026 (Wed)</t>
         </is>
       </c>
       <c r="G18" s="15" t="n">
@@ -25418,7 +25418,7 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>17-Mar-2026 (Tue)</t>
+          <t>19-Mar-2026 (Thu)</t>
         </is>
       </c>
       <c r="J18" s="15" t="n">
@@ -25479,7 +25479,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>12-Mar-2026 (Thu)</t>
+          <t>18-Mar-2026 (Wed)</t>
         </is>
       </c>
       <c r="G19" s="15" t="n">
@@ -25492,7 +25492,7 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>26-Mar-2026 (Thu)</t>
+          <t>27-Mar-2026 (Fri)</t>
         </is>
       </c>
       <c r="J19" s="15" t="n">
@@ -25553,7 +25553,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>19-Jan-2026 (Mon)</t>
+          <t>20-Jan-2026 (Tue)</t>
         </is>
       </c>
       <c r="G20" s="15" t="n">
@@ -25566,7 +25566,7 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>30-Jan-2026 (Fri)</t>
+          <t>29-Jan-2026 (Thu)</t>
         </is>
       </c>
       <c r="J20" s="15" t="n">
@@ -25627,7 +25627,7 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>10-Mar-2026 (Tue)</t>
+          <t>16-Mar-2026 (Mon)</t>
         </is>
       </c>
       <c r="G21" s="15" t="n">
@@ -25701,7 +25701,7 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>12-Feb-2026 (Thu)</t>
+          <t>13-Feb-2026 (Fri)</t>
         </is>
       </c>
       <c r="G22" s="15" t="n">
@@ -25714,7 +25714,7 @@
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>20-Feb-2026 (Fri)</t>
+          <t>23-Feb-2026 (Mon)</t>
         </is>
       </c>
       <c r="J22" s="15" t="n">
@@ -25775,7 +25775,7 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>12-Feb-2026 (Thu)</t>
+          <t>13-Feb-2026 (Fri)</t>
         </is>
       </c>
       <c r="G23" s="15" t="n">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>18-Feb-2026 (Wed)</t>
+          <t>23-Feb-2026 (Mon)</t>
         </is>
       </c>
       <c r="J23" s="15" t="n">
@@ -25849,7 +25849,7 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>16-Feb-2026 (Mon)</t>
+          <t>18-Feb-2026 (Wed)</t>
         </is>
       </c>
       <c r="G24" s="15" t="n">
@@ -25862,7 +25862,7 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>24-Feb-2026 (Tue)</t>
+          <t>26-Feb-2026 (Thu)</t>
         </is>
       </c>
       <c r="J24" s="15" t="n">
@@ -25923,7 +25923,7 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>15-Jan-2026 (Thu)</t>
+          <t>20-Jan-2026 (Tue)</t>
         </is>
       </c>
       <c r="G25" s="15" t="n">
@@ -25936,7 +25936,7 @@
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>28-Jan-2026 (Wed)</t>
+          <t>29-Jan-2026 (Thu)</t>
         </is>
       </c>
       <c r="J25" s="15" t="n">
@@ -25997,7 +25997,7 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>10-Feb-2026 (Tue)</t>
+          <t>13-Feb-2026 (Fri)</t>
         </is>
       </c>
       <c r="G26" s="15" t="n">
@@ -26010,7 +26010,7 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>20-Feb-2026 (Fri)</t>
+          <t>23-Feb-2026 (Mon)</t>
         </is>
       </c>
       <c r="J26" s="15" t="n">
@@ -26071,7 +26071,7 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>05-Jan-2026 (Mon)</t>
+          <t>09-Jan-2026 (Fri)</t>
         </is>
       </c>
       <c r="G27" s="15" t="n">
@@ -26084,7 +26084,7 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>16-Jan-2026 (Fri)</t>
+          <t>19-Jan-2026 (Mon)</t>
         </is>
       </c>
       <c r="J27" s="15" t="n">
@@ -26145,7 +26145,7 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>06-Mar-2026 (Fri)</t>
+          <t>11-Mar-2026 (Wed)</t>
         </is>
       </c>
       <c r="G28" s="15" t="n">
@@ -26158,7 +26158,7 @@
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>23-Mar-2026 (Mon)</t>
+          <t>19-Mar-2026 (Thu)</t>
         </is>
       </c>
       <c r="J28" s="15" t="n">
@@ -26219,7 +26219,7 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>05-Jan-2026 (Mon)</t>
+          <t>07-Jan-2026 (Wed)</t>
         </is>
       </c>
       <c r="G29" s="15" t="n">
@@ -26232,7 +26232,7 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>13-Jan-2026 (Tue)</t>
+          <t>15-Jan-2026 (Thu)</t>
         </is>
       </c>
       <c r="J29" s="15" t="n">
@@ -26293,7 +26293,7 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>09-Mar-2026 (Mon)</t>
+          <t>10-Mar-2026 (Tue)</t>
         </is>
       </c>
       <c r="G30" s="15" t="n">
@@ -26306,7 +26306,7 @@
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>13-Mar-2026 (Fri)</t>
+          <t>18-Mar-2026 (Wed)</t>
         </is>
       </c>
       <c r="J30" s="15" t="n">
@@ -26367,7 +26367,7 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>17-Feb-2026 (Tue)</t>
+          <t>19-Feb-2026 (Thu)</t>
         </is>
       </c>
       <c r="G31" s="15" t="n">
@@ -26380,7 +26380,7 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>02-Mar-2026 (Mon)</t>
+          <t>27-Feb-2026 (Fri)</t>
         </is>
       </c>
       <c r="J31" s="15" t="n">
@@ -26515,7 +26515,7 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>04-Mar-2026 (Wed)</t>
+          <t>11-Mar-2026 (Wed)</t>
         </is>
       </c>
       <c r="G33" s="15" t="n">
@@ -26528,7 +26528,7 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>17-Mar-2026 (Tue)</t>
+          <t>19-Mar-2026 (Thu)</t>
         </is>
       </c>
       <c r="J33" s="15" t="n">
@@ -26589,7 +26589,7 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>13-Mar-2026 (Fri)</t>
+          <t>16-Mar-2026 (Mon)</t>
         </is>
       </c>
       <c r="G34" s="15" t="n">
@@ -26602,7 +26602,7 @@
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>23-Mar-2026 (Mon)</t>
+          <t>24-Mar-2026 (Tue)</t>
         </is>
       </c>
       <c r="J34" s="15" t="n">
@@ -26663,7 +26663,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>09-Mar-2026 (Mon)</t>
+          <t>10-Mar-2026 (Tue)</t>
         </is>
       </c>
       <c r="G35" s="15" t="n">
@@ -26676,7 +26676,7 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>17-Mar-2026 (Tue)</t>
+          <t>18-Mar-2026 (Wed)</t>
         </is>
       </c>
       <c r="J35" s="15" t="n">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>09-Mar-2026 (Mon)</t>
+          <t>10-Mar-2026 (Tue)</t>
         </is>
       </c>
       <c r="G36" s="15" t="n">
@@ -26750,7 +26750,7 @@
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>13-Mar-2026 (Fri)</t>
+          <t>18-Mar-2026 (Wed)</t>
         </is>
       </c>
       <c r="J36" s="15" t="n">
@@ -26811,7 +26811,7 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>12-Mar-2026 (Thu)</t>
+          <t>16-Mar-2026 (Mon)</t>
         </is>
       </c>
       <c r="G37" s="15" t="n">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>26-Mar-2026 (Thu)</t>
+          <t>24-Mar-2026 (Tue)</t>
         </is>
       </c>
       <c r="J37" s="15" t="n">
@@ -26972,7 +26972,7 @@
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>27-Feb-2026 (Fri)</t>
+          <t>26-Feb-2026 (Thu)</t>
         </is>
       </c>
       <c r="J39" s="15" t="n">
@@ -27033,7 +27033,7 @@
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>05-Feb-2026 (Thu)</t>
+          <t>11-Feb-2026 (Wed)</t>
         </is>
       </c>
       <c r="G40" s="15" t="n">
@@ -27107,7 +27107,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>04-Feb-2026 (Wed)</t>
+          <t>09-Feb-2026 (Mon)</t>
         </is>
       </c>
       <c r="G41" s="15" t="n">
@@ -27194,7 +27194,7 @@
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>19-Jan-2026 (Mon)</t>
+          <t>22-Jan-2026 (Thu)</t>
         </is>
       </c>
       <c r="J42" s="15" t="n">
@@ -27403,7 +27403,7 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>15-Jan-2026 (Thu)</t>
+          <t>20-Jan-2026 (Tue)</t>
         </is>
       </c>
       <c r="G45" s="15" t="n">
@@ -27416,7 +27416,7 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>28-Jan-2026 (Wed)</t>
+          <t>29-Jan-2026 (Thu)</t>
         </is>
       </c>
       <c r="J45" s="15" t="n">
@@ -27490,7 +27490,7 @@
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>12-Feb-2026 (Thu)</t>
+          <t>17-Feb-2026 (Tue)</t>
         </is>
       </c>
       <c r="J46" s="15" t="n">
@@ -27564,7 +27564,7 @@
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>23-Mar-2026 (Mon)</t>
+          <t>19-Mar-2026 (Thu)</t>
         </is>
       </c>
       <c r="J47" s="15" t="n">
@@ -27638,7 +27638,7 @@
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>19-Jan-2026 (Mon)</t>
+          <t>22-Jan-2026 (Thu)</t>
         </is>
       </c>
       <c r="J48" s="15" t="n">
@@ -27699,7 +27699,7 @@
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>06-Mar-2026 (Fri)</t>
+          <t>11-Mar-2026 (Wed)</t>
         </is>
       </c>
       <c r="G49" s="15" t="n">
@@ -27712,7 +27712,7 @@
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>23-Mar-2026 (Mon)</t>
+          <t>19-Mar-2026 (Thu)</t>
         </is>
       </c>
       <c r="J49" s="15" t="n">
@@ -27847,7 +27847,7 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>07-Jan-2026 (Wed)</t>
+          <t>09-Jan-2026 (Fri)</t>
         </is>
       </c>
       <c r="G51" s="15" t="n">
@@ -27860,7 +27860,7 @@
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>20-Jan-2026 (Tue)</t>
+          <t>19-Jan-2026 (Mon)</t>
         </is>
       </c>
       <c r="J51" s="15" t="n">
@@ -27934,7 +27934,7 @@
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>27-Feb-2026 (Fri)</t>
+          <t>26-Feb-2026 (Thu)</t>
         </is>
       </c>
       <c r="J52" s="15" t="n">
@@ -27995,7 +27995,7 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>31-Dec-2025 (Wed)</t>
+          <t>07-Jan-2026 (Wed)</t>
         </is>
       </c>
       <c r="G53" s="15" t="n">
@@ -28008,7 +28008,7 @@
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>13-Jan-2026 (Tue)</t>
+          <t>15-Jan-2026 (Thu)</t>
         </is>
       </c>
       <c r="J53" s="15" t="n">
@@ -28069,7 +28069,7 @@
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>04-Feb-2026 (Wed)</t>
+          <t>09-Feb-2026 (Mon)</t>
         </is>
       </c>
       <c r="G54" s="15" t="n">
@@ -28301,7 +28301,7 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>20-Oct-2025 (Mon)</t>
+          <t>17-Oct-2025 (Fri)</t>
         </is>
       </c>
       <c r="J5" s="15" t="n">
@@ -28362,7 +28362,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>04-Dec-2025 (Thu)</t>
+          <t>10-Dec-2025 (Wed)</t>
         </is>
       </c>
       <c r="G6" s="15" t="n">
@@ -28375,7 +28375,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>16-Dec-2025 (Tue)</t>
+          <t>18-Dec-2025 (Thu)</t>
         </is>
       </c>
       <c r="J6" s="15" t="n">
@@ -28449,7 +28449,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>26-Dec-2025 (Fri)</t>
+          <t>24-Dec-2025 (Wed)</t>
         </is>
       </c>
       <c r="J7" s="15" t="n">
@@ -28510,7 +28510,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>17-Nov-2025 (Mon)</t>
+          <t>19-Nov-2025 (Wed)</t>
         </is>
       </c>
       <c r="G8" s="15" t="n">
@@ -28523,7 +28523,7 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>25-Nov-2025 (Tue)</t>
+          <t>27-Nov-2025 (Thu)</t>
         </is>
       </c>
       <c r="J8" s="15" t="n">
@@ -28584,7 +28584,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>07-Oct-2025 (Tue)</t>
+          <t>08-Oct-2025 (Wed)</t>
         </is>
       </c>
       <c r="G9" s="15" t="n">
@@ -28597,7 +28597,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>17-Oct-2025 (Fri)</t>
+          <t>16-Oct-2025 (Thu)</t>
         </is>
       </c>
       <c r="J9" s="15" t="n">
@@ -28658,7 +28658,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>03-Nov-2025 (Mon)</t>
+          <t>07-Nov-2025 (Fri)</t>
         </is>
       </c>
       <c r="G10" s="15" t="n">
@@ -28671,7 +28671,7 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>13-Nov-2025 (Thu)</t>
+          <t>17-Nov-2025 (Mon)</t>
         </is>
       </c>
       <c r="J10" s="15" t="n">
@@ -28732,7 +28732,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>14-Oct-2025 (Tue)</t>
+          <t>15-Oct-2025 (Wed)</t>
         </is>
       </c>
       <c r="G11" s="15" t="n">
@@ -28806,7 +28806,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>08-Dec-2025 (Mon)</t>
+          <t>11-Dec-2025 (Thu)</t>
         </is>
       </c>
       <c r="G12" s="15" t="n">
@@ -28819,7 +28819,7 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>18-Dec-2025 (Thu)</t>
+          <t>19-Dec-2025 (Fri)</t>
         </is>
       </c>
       <c r="J12" s="15" t="n">
@@ -28893,7 +28893,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>26-Dec-2025 (Fri)</t>
+          <t>30-Dec-2025 (Tue)</t>
         </is>
       </c>
       <c r="J13" s="15" t="n">
@@ -29028,7 +29028,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>10-Oct-2025 (Fri)</t>
+          <t>17-Oct-2025 (Fri)</t>
         </is>
       </c>
       <c r="G15" s="15" t="n">
@@ -29102,7 +29102,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>04-Dec-2025 (Thu)</t>
+          <t>10-Dec-2025 (Wed)</t>
         </is>
       </c>
       <c r="G16" s="15" t="n">
@@ -29176,7 +29176,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>06-Oct-2025 (Mon)</t>
+          <t>09-Oct-2025 (Thu)</t>
         </is>
       </c>
       <c r="G17" s="15" t="n">
@@ -29189,7 +29189,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>20-Oct-2025 (Mon)</t>
+          <t>17-Oct-2025 (Fri)</t>
         </is>
       </c>
       <c r="J17" s="15" t="n">
@@ -29250,7 +29250,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>04-Nov-2025 (Tue)</t>
+          <t>12-Nov-2025 (Wed)</t>
         </is>
       </c>
       <c r="G18" s="15" t="n">
@@ -29263,7 +29263,7 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>21-Nov-2025 (Fri)</t>
+          <t>20-Nov-2025 (Thu)</t>
         </is>
       </c>
       <c r="J18" s="15" t="n">
@@ -29324,7 +29324,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>11-Dec-2025 (Thu)</t>
+          <t>16-Dec-2025 (Tue)</t>
         </is>
       </c>
       <c r="G19" s="15" t="n">
@@ -29337,7 +29337,7 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>26-Dec-2025 (Fri)</t>
+          <t>24-Dec-2025 (Wed)</t>
         </is>
       </c>
       <c r="J19" s="15" t="n">
@@ -29398,7 +29398,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>03-Oct-2025 (Fri)</t>
+          <t>08-Oct-2025 (Wed)</t>
         </is>
       </c>
       <c r="G20" s="15" t="n">
@@ -29411,7 +29411,7 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>15-Oct-2025 (Wed)</t>
+          <t>16-Oct-2025 (Thu)</t>
         </is>
       </c>
       <c r="J20" s="15" t="n">
@@ -29472,7 +29472,7 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>10-Dec-2025 (Wed)</t>
+          <t>11-Dec-2025 (Thu)</t>
         </is>
       </c>
       <c r="G21" s="15" t="n">
@@ -29485,7 +29485,7 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>22-Dec-2025 (Mon)</t>
+          <t>19-Dec-2025 (Fri)</t>
         </is>
       </c>
       <c r="J21" s="15" t="n">
@@ -29546,7 +29546,7 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>11-Nov-2025 (Tue)</t>
+          <t>13-Nov-2025 (Thu)</t>
         </is>
       </c>
       <c r="G22" s="15" t="n">
@@ -29559,7 +29559,7 @@
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>18-Nov-2025 (Tue)</t>
+          <t>21-Nov-2025 (Fri)</t>
         </is>
       </c>
       <c r="J22" s="15" t="n">
@@ -29620,7 +29620,7 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>10-Dec-2025 (Wed)</t>
+          <t>11-Dec-2025 (Thu)</t>
         </is>
       </c>
       <c r="G23" s="15" t="n">
@@ -29633,7 +29633,7 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>16-Dec-2025 (Tue)</t>
+          <t>19-Dec-2025 (Fri)</t>
         </is>
       </c>
       <c r="J23" s="15" t="n">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>10-Dec-2025 (Wed)</t>
+          <t>11-Dec-2025 (Thu)</t>
         </is>
       </c>
       <c r="G24" s="15" t="n">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>18-Dec-2025 (Thu)</t>
+          <t>19-Dec-2025 (Fri)</t>
         </is>
       </c>
       <c r="J24" s="15" t="n">
@@ -29842,7 +29842,7 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>01-Oct-2025 (Wed)</t>
+          <t>09-Oct-2025 (Thu)</t>
         </is>
       </c>
       <c r="G26" s="15" t="n">
@@ -29855,7 +29855,7 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>15-Oct-2025 (Wed)</t>
+          <t>17-Oct-2025 (Fri)</t>
         </is>
       </c>
       <c r="J26" s="15" t="n">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>08-Dec-2025 (Mon)</t>
+          <t>10-Dec-2025 (Wed)</t>
         </is>
       </c>
       <c r="G27" s="15" t="n">
@@ -29929,7 +29929,7 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>15-Dec-2025 (Mon)</t>
+          <t>18-Dec-2025 (Thu)</t>
         </is>
       </c>
       <c r="J27" s="15" t="n">
@@ -30003,7 +30003,7 @@
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>23-Oct-2025 (Thu)</t>
+          <t>22-Oct-2025 (Wed)</t>
         </is>
       </c>
       <c r="J28" s="15" t="n">
@@ -30064,7 +30064,7 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>07-Nov-2025 (Fri)</t>
+          <t>13-Nov-2025 (Thu)</t>
         </is>
       </c>
       <c r="G29" s="15" t="n">
@@ -30138,7 +30138,7 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>13-Nov-2025 (Thu)</t>
+          <t>18-Nov-2025 (Tue)</t>
         </is>
       </c>
       <c r="G30" s="15" t="n">
@@ -30151,7 +30151,7 @@
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>25-Nov-2025 (Tue)</t>
+          <t>26-Nov-2025 (Wed)</t>
         </is>
       </c>
       <c r="J30" s="15" t="n">
@@ -30212,7 +30212,7 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>08-Dec-2025 (Mon)</t>
+          <t>10-Dec-2025 (Wed)</t>
         </is>
       </c>
       <c r="G31" s="15" t="n">
@@ -30225,7 +30225,7 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>17-Dec-2025 (Wed)</t>
+          <t>18-Dec-2025 (Thu)</t>
         </is>
       </c>
       <c r="J31" s="15" t="n">
@@ -30286,7 +30286,7 @@
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>11-Nov-2025 (Tue)</t>
+          <t>13-Nov-2025 (Thu)</t>
         </is>
       </c>
       <c r="G32" s="15" t="n">
@@ -30299,7 +30299,7 @@
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>20-Nov-2025 (Thu)</t>
+          <t>21-Nov-2025 (Fri)</t>
         </is>
       </c>
       <c r="J32" s="15" t="n">
@@ -30360,7 +30360,7 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>10-Oct-2025 (Fri)</t>
+          <t>17-Oct-2025 (Fri)</t>
         </is>
       </c>
       <c r="G33" s="15" t="n">
@@ -30373,7 +30373,7 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>24-Oct-2025 (Fri)</t>
+          <t>28-Oct-2025 (Tue)</t>
         </is>
       </c>
       <c r="J33" s="15" t="n">
@@ -30434,7 +30434,7 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>09-Oct-2025 (Thu)</t>
+          <t>14-Oct-2025 (Tue)</t>
         </is>
       </c>
       <c r="G34" s="15" t="n">
@@ -30447,7 +30447,7 @@
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>20-Oct-2025 (Mon)</t>
+          <t>23-Oct-2025 (Thu)</t>
         </is>
       </c>
       <c r="J34" s="15" t="n">
@@ -30508,7 +30508,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>11-Dec-2025 (Thu)</t>
+          <t>17-Dec-2025 (Wed)</t>
         </is>
       </c>
       <c r="G35" s="15" t="n">
@@ -30521,7 +30521,7 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>24-Dec-2025 (Wed)</t>
+          <t>25-Dec-2025 (Thu)</t>
         </is>
       </c>
       <c r="J35" s="15" t="n">
@@ -30582,7 +30582,7 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>11-Dec-2025 (Thu)</t>
+          <t>16-Dec-2025 (Tue)</t>
         </is>
       </c>
       <c r="G36" s="15" t="n">
@@ -30595,7 +30595,7 @@
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>26-Dec-2025 (Fri)</t>
+          <t>24-Dec-2025 (Wed)</t>
         </is>
       </c>
       <c r="J36" s="15" t="n">
@@ -30656,7 +30656,7 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>10-Oct-2025 (Fri)</t>
+          <t>17-Oct-2025 (Fri)</t>
         </is>
       </c>
       <c r="G37" s="15" t="n">
@@ -30730,7 +30730,7 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>13-Oct-2025 (Mon)</t>
+          <t>14-Oct-2025 (Tue)</t>
         </is>
       </c>
       <c r="G38" s="15" t="n">
@@ -30743,7 +30743,7 @@
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>20-Oct-2025 (Mon)</t>
+          <t>23-Oct-2025 (Thu)</t>
         </is>
       </c>
       <c r="J38" s="15" t="n">
@@ -30952,7 +30952,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>09-Dec-2025 (Tue)</t>
+          <t>16-Dec-2025 (Tue)</t>
         </is>
       </c>
       <c r="G41" s="15" t="n">
@@ -30965,7 +30965,7 @@
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>22-Dec-2025 (Mon)</t>
+          <t>24-Dec-2025 (Wed)</t>
         </is>
       </c>
       <c r="J41" s="15" t="n">
@@ -31026,7 +31026,7 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>08-Dec-2025 (Mon)</t>
+          <t>10-Dec-2025 (Wed)</t>
         </is>
       </c>
       <c r="G42" s="15" t="n">
@@ -31039,7 +31039,7 @@
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>15-Dec-2025 (Mon)</t>
+          <t>18-Dec-2025 (Thu)</t>
         </is>
       </c>
       <c r="J42" s="15" t="n">
@@ -31100,7 +31100,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>17-Nov-2025 (Mon)</t>
+          <t>18-Nov-2025 (Tue)</t>
         </is>
       </c>
       <c r="G43" s="15" t="n">
@@ -31113,7 +31113,7 @@
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>25-Nov-2025 (Tue)</t>
+          <t>26-Nov-2025 (Wed)</t>
         </is>
       </c>
       <c r="J43" s="15" t="n">
@@ -31174,7 +31174,7 @@
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>06-Oct-2025 (Mon)</t>
+          <t>09-Oct-2025 (Thu)</t>
         </is>
       </c>
       <c r="G44" s="15" t="n">
@@ -31187,7 +31187,7 @@
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>20-Oct-2025 (Mon)</t>
+          <t>17-Oct-2025 (Fri)</t>
         </is>
       </c>
       <c r="J44" s="15" t="n">
@@ -31248,7 +31248,7 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>31-Oct-2025 (Fri)</t>
+          <t>07-Nov-2025 (Fri)</t>
         </is>
       </c>
       <c r="G45" s="15" t="n">
@@ -31261,7 +31261,7 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>14-Nov-2025 (Fri)</t>
+          <t>17-Nov-2025 (Mon)</t>
         </is>
       </c>
       <c r="J45" s="15" t="n">
@@ -31322,7 +31322,7 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>06-Nov-2025 (Thu)</t>
+          <t>07-Nov-2025 (Fri)</t>
         </is>
       </c>
       <c r="G46" s="15" t="n">
@@ -31335,7 +31335,7 @@
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>13-Nov-2025 (Thu)</t>
+          <t>17-Nov-2025 (Mon)</t>
         </is>
       </c>
       <c r="J46" s="15" t="n">
@@ -31396,7 +31396,7 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>14-Nov-2025 (Fri)</t>
+          <t>19-Nov-2025 (Wed)</t>
         </is>
       </c>
       <c r="G47" s="15" t="n">
@@ -31409,7 +31409,7 @@
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>28-Nov-2025 (Fri)</t>
+          <t>27-Nov-2025 (Thu)</t>
         </is>
       </c>
       <c r="J47" s="15" t="n">
@@ -31470,7 +31470,7 @@
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>10-Oct-2025 (Fri)</t>
+          <t>17-Oct-2025 (Fri)</t>
         </is>
       </c>
       <c r="G48" s="15" t="n">
@@ -31544,7 +31544,7 @@
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>12-Dec-2025 (Fri)</t>
+          <t>16-Dec-2025 (Tue)</t>
         </is>
       </c>
       <c r="G49" s="15" t="n">
@@ -31557,7 +31557,7 @@
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>22-Dec-2025 (Mon)</t>
+          <t>24-Dec-2025 (Wed)</t>
         </is>
       </c>
       <c r="J49" s="15" t="n">
@@ -31618,7 +31618,7 @@
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>31-Oct-2025 (Fri)</t>
+          <t>07-Nov-2025 (Fri)</t>
         </is>
       </c>
       <c r="G50" s="15" t="n">
@@ -31631,7 +31631,7 @@
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>14-Nov-2025 (Fri)</t>
+          <t>17-Nov-2025 (Mon)</t>
         </is>
       </c>
       <c r="J50" s="15" t="n">
@@ -31692,7 +31692,7 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>13-Oct-2025 (Mon)</t>
+          <t>14-Oct-2025 (Tue)</t>
         </is>
       </c>
       <c r="G51" s="15" t="n">
@@ -31705,7 +31705,7 @@
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>20-Oct-2025 (Mon)</t>
+          <t>23-Oct-2025 (Thu)</t>
         </is>
       </c>
       <c r="J51" s="15" t="n">
@@ -31766,7 +31766,7 @@
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>17-Nov-2025 (Mon)</t>
+          <t>18-Nov-2025 (Tue)</t>
         </is>
       </c>
       <c r="G52" s="15" t="n">
@@ -31779,7 +31779,7 @@
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>25-Nov-2025 (Tue)</t>
+          <t>26-Nov-2025 (Wed)</t>
         </is>
       </c>
       <c r="J52" s="15" t="n">
@@ -31840,7 +31840,7 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>07-Oct-2025 (Tue)</t>
+          <t>08-Oct-2025 (Wed)</t>
         </is>
       </c>
       <c r="G53" s="15" t="n">
@@ -31853,7 +31853,7 @@
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>13-Oct-2025 (Mon)</t>
+          <t>16-Oct-2025 (Thu)</t>
         </is>
       </c>
       <c r="J53" s="15" t="n">
@@ -31914,7 +31914,7 @@
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>10-Dec-2025 (Wed)</t>
+          <t>11-Dec-2025 (Thu)</t>
         </is>
       </c>
       <c r="G54" s="15" t="n">
@@ -31927,7 +31927,7 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>22-Dec-2025 (Mon)</t>
+          <t>19-Dec-2025 (Fri)</t>
         </is>
       </c>
       <c r="J54" s="15" t="n">
@@ -32133,7 +32133,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>08-Jul-2025 (Tue)</t>
+          <t>09-Jul-2025 (Wed)</t>
         </is>
       </c>
       <c r="G5" s="15" t="n">
@@ -32146,7 +32146,7 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>16-Jul-2025 (Wed)</t>
+          <t>17-Jul-2025 (Thu)</t>
         </is>
       </c>
       <c r="J5" s="15" t="n">
@@ -32281,7 +32281,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>15-Sep-2025 (Mon)</t>
+          <t>16-Sep-2025 (Tue)</t>
         </is>
       </c>
       <c r="G7" s="15" t="n">
@@ -32294,7 +32294,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>23-Sep-2025 (Tue)</t>
+          <t>24-Sep-2025 (Wed)</t>
         </is>
       </c>
       <c r="J7" s="15" t="n">
@@ -32368,7 +32368,7 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>19-Aug-2025 (Tue)</t>
+          <t>18-Aug-2025 (Mon)</t>
         </is>
       </c>
       <c r="J8" s="15" t="n">
@@ -32429,7 +32429,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>19-Sep-2025 (Fri)</t>
+          <t>22-Sep-2025 (Mon)</t>
         </is>
       </c>
       <c r="G9" s="15" t="n">
@@ -32442,7 +32442,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>26-Sep-2025 (Fri)</t>
+          <t>30-Sep-2025 (Tue)</t>
         </is>
       </c>
       <c r="J9" s="15" t="n">
@@ -32503,7 +32503,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>11-Jul-2025 (Fri)</t>
+          <t>18-Jul-2025 (Fri)</t>
         </is>
       </c>
       <c r="G10" s="15" t="n">
@@ -32516,7 +32516,7 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>29-Jul-2025 (Tue)</t>
+          <t>28-Jul-2025 (Mon)</t>
         </is>
       </c>
       <c r="J10" s="15" t="n">
@@ -32577,7 +32577,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>14-Aug-2025 (Thu)</t>
+          <t>20-Aug-2025 (Wed)</t>
         </is>
       </c>
       <c r="G11" s="15" t="n">
@@ -32651,7 +32651,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>11-Aug-2025 (Mon)</t>
+          <t>18-Aug-2025 (Mon)</t>
         </is>
       </c>
       <c r="G12" s="15" t="n">
@@ -32799,7 +32799,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>15-Sep-2025 (Mon)</t>
+          <t>16-Sep-2025 (Tue)</t>
         </is>
       </c>
       <c r="G14" s="15" t="n">
@@ -32812,7 +32812,7 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>25-Sep-2025 (Thu)</t>
+          <t>24-Sep-2025 (Wed)</t>
         </is>
       </c>
       <c r="J14" s="15" t="n">
@@ -32873,7 +32873,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>15-Sep-2025 (Mon)</t>
+          <t>16-Sep-2025 (Tue)</t>
         </is>
       </c>
       <c r="G15" s="15" t="n">
@@ -32886,7 +32886,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>25-Sep-2025 (Thu)</t>
+          <t>24-Sep-2025 (Wed)</t>
         </is>
       </c>
       <c r="J15" s="15" t="n">
@@ -32947,7 +32947,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>08-Jul-2025 (Tue)</t>
+          <t>09-Jul-2025 (Wed)</t>
         </is>
       </c>
       <c r="G16" s="15" t="n">
@@ -32960,7 +32960,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>18-Jul-2025 (Fri)</t>
+          <t>17-Jul-2025 (Thu)</t>
         </is>
       </c>
       <c r="J16" s="15" t="n">
@@ -33021,7 +33021,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>07-Aug-2025 (Thu)</t>
+          <t>12-Aug-2025 (Tue)</t>
         </is>
       </c>
       <c r="G17" s="15" t="n">
@@ -33095,7 +33095,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>05-Sep-2025 (Fri)</t>
+          <t>11-Sep-2025 (Thu)</t>
         </is>
       </c>
       <c r="G18" s="15" t="n">
@@ -33108,7 +33108,7 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>17-Sep-2025 (Wed)</t>
+          <t>19-Sep-2025 (Fri)</t>
         </is>
       </c>
       <c r="J18" s="15" t="n">
@@ -33169,7 +33169,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>07-Jul-2025 (Mon)</t>
+          <t>14-Jul-2025 (Mon)</t>
         </is>
       </c>
       <c r="G19" s="15" t="n">
@@ -33182,7 +33182,7 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>18-Jul-2025 (Fri)</t>
+          <t>22-Jul-2025 (Tue)</t>
         </is>
       </c>
       <c r="J19" s="15" t="n">
@@ -33243,7 +33243,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>09-Sep-2025 (Tue)</t>
+          <t>11-Sep-2025 (Thu)</t>
         </is>
       </c>
       <c r="G20" s="15" t="n">
@@ -33256,7 +33256,7 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>18-Sep-2025 (Thu)</t>
+          <t>19-Sep-2025 (Fri)</t>
         </is>
       </c>
       <c r="J20" s="15" t="n">
@@ -33317,7 +33317,7 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>02-Jul-2025 (Wed)</t>
+          <t>08-Jul-2025 (Tue)</t>
         </is>
       </c>
       <c r="G21" s="15" t="n">
@@ -33330,7 +33330,7 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>14-Jul-2025 (Mon)</t>
+          <t>16-Jul-2025 (Wed)</t>
         </is>
       </c>
       <c r="J21" s="15" t="n">
@@ -33391,7 +33391,7 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>10-Sep-2025 (Wed)</t>
+          <t>17-Sep-2025 (Wed)</t>
         </is>
       </c>
       <c r="G22" s="15" t="n">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>23-Sep-2025 (Tue)</t>
+          <t>25-Sep-2025 (Thu)</t>
         </is>
       </c>
       <c r="J22" s="15" t="n">
@@ -33465,7 +33465,7 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>09-Sep-2025 (Tue)</t>
+          <t>11-Sep-2025 (Thu)</t>
         </is>
       </c>
       <c r="G23" s="15" t="n">
@@ -33478,7 +33478,7 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>16-Sep-2025 (Tue)</t>
+          <t>19-Sep-2025 (Fri)</t>
         </is>
       </c>
       <c r="J23" s="15" t="n">
@@ -33539,7 +33539,7 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>03-Sep-2025 (Wed)</t>
+          <t>10-Sep-2025 (Wed)</t>
         </is>
       </c>
       <c r="G24" s="15" t="n">
@@ -33552,7 +33552,7 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>19-Sep-2025 (Fri)</t>
+          <t>18-Sep-2025 (Thu)</t>
         </is>
       </c>
       <c r="J24" s="15" t="n">
@@ -33687,7 +33687,7 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>05-Sep-2025 (Fri)</t>
+          <t>10-Sep-2025 (Wed)</t>
         </is>
       </c>
       <c r="G26" s="15" t="n">
@@ -33761,7 +33761,7 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>11-Jul-2025 (Fri)</t>
+          <t>18-Jul-2025 (Fri)</t>
         </is>
       </c>
       <c r="G27" s="15" t="n">
@@ -33774,7 +33774,7 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>29-Jul-2025 (Tue)</t>
+          <t>28-Jul-2025 (Mon)</t>
         </is>
       </c>
       <c r="J27" s="15" t="n">
@@ -33835,7 +33835,7 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>08-Jul-2025 (Tue)</t>
+          <t>09-Jul-2025 (Wed)</t>
         </is>
       </c>
       <c r="G28" s="15" t="n">
@@ -33848,7 +33848,7 @@
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>14-Jul-2025 (Mon)</t>
+          <t>17-Jul-2025 (Thu)</t>
         </is>
       </c>
       <c r="J28" s="15" t="n">
@@ -33909,7 +33909,7 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>15-Sep-2025 (Mon)</t>
+          <t>16-Sep-2025 (Tue)</t>
         </is>
       </c>
       <c r="G29" s="15" t="n">
@@ -33922,7 +33922,7 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>19-Sep-2025 (Fri)</t>
+          <t>24-Sep-2025 (Wed)</t>
         </is>
       </c>
       <c r="J29" s="15" t="n">
@@ -33983,7 +33983,7 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>05-Aug-2025 (Tue)</t>
+          <t>12-Aug-2025 (Tue)</t>
         </is>
       </c>
       <c r="G30" s="15" t="n">
@@ -33996,7 +33996,7 @@
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>22-Aug-2025 (Fri)</t>
+          <t>21-Aug-2025 (Thu)</t>
         </is>
       </c>
       <c r="J30" s="15" t="n">
@@ -34057,7 +34057,7 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>10-Jul-2025 (Thu)</t>
+          <t>14-Jul-2025 (Mon)</t>
         </is>
       </c>
       <c r="G31" s="15" t="n">
@@ -34070,7 +34070,7 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>18-Jul-2025 (Fri)</t>
+          <t>22-Jul-2025 (Tue)</t>
         </is>
       </c>
       <c r="J31" s="15" t="n">
@@ -34131,7 +34131,7 @@
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>13-Aug-2025 (Wed)</t>
+          <t>18-Aug-2025 (Mon)</t>
         </is>
       </c>
       <c r="G32" s="15" t="n">
@@ -34144,7 +34144,7 @@
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>25-Aug-2025 (Mon)</t>
+          <t>26-Aug-2025 (Tue)</t>
         </is>
       </c>
       <c r="J32" s="15" t="n">
@@ -34205,7 +34205,7 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>02-Jul-2025 (Wed)</t>
+          <t>08-Jul-2025 (Tue)</t>
         </is>
       </c>
       <c r="G33" s="15" t="n">
@@ -34279,7 +34279,7 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>08-Aug-2025 (Fri)</t>
+          <t>12-Aug-2025 (Tue)</t>
         </is>
       </c>
       <c r="G34" s="15" t="n">
@@ -34292,7 +34292,7 @@
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>22-Aug-2025 (Fri)</t>
+          <t>21-Aug-2025 (Thu)</t>
         </is>
       </c>
       <c r="J34" s="15" t="n">
@@ -34353,7 +34353,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>10-Jul-2025 (Thu)</t>
+          <t>14-Jul-2025 (Mon)</t>
         </is>
       </c>
       <c r="G35" s="15" t="n">
@@ -34366,7 +34366,7 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>18-Jul-2025 (Fri)</t>
+          <t>22-Jul-2025 (Tue)</t>
         </is>
       </c>
       <c r="J35" s="15" t="n">
@@ -34427,7 +34427,7 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>13-Aug-2025 (Wed)</t>
+          <t>18-Aug-2025 (Mon)</t>
         </is>
       </c>
       <c r="G36" s="15" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>25-Aug-2025 (Mon)</t>
+          <t>26-Aug-2025 (Tue)</t>
         </is>
       </c>
       <c r="J36" s="15" t="n">
@@ -34514,7 +34514,7 @@
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>15-Sep-2025 (Mon)</t>
+          <t>18-Sep-2025 (Thu)</t>
         </is>
       </c>
       <c r="J37" s="15" t="n">
@@ -34588,7 +34588,7 @@
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>23-Jul-2025 (Wed)</t>
+          <t>22-Jul-2025 (Tue)</t>
         </is>
       </c>
       <c r="J38" s="15" t="n">
@@ -34649,7 +34649,7 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>19-Aug-2025 (Tue)</t>
+          <t>20-Aug-2025 (Wed)</t>
         </is>
       </c>
       <c r="G39" s="15" t="n">
@@ -34662,7 +34662,7 @@
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>01-Sep-2025 (Mon)</t>
+          <t>28-Aug-2025 (Thu)</t>
         </is>
       </c>
       <c r="J39" s="15" t="n">
@@ -34736,7 +34736,7 @@
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>18-Aug-2025 (Mon)</t>
+          <t>21-Aug-2025 (Thu)</t>
         </is>
       </c>
       <c r="J40" s="15" t="n">
@@ -34797,7 +34797,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>04-Jul-2025 (Fri)</t>
+          <t>08-Jul-2025 (Tue)</t>
         </is>
       </c>
       <c r="G41" s="15" t="n">
@@ -34810,7 +34810,7 @@
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>11-Jul-2025 (Fri)</t>
+          <t>16-Jul-2025 (Wed)</t>
         </is>
       </c>
       <c r="J41" s="15" t="n">
@@ -34871,7 +34871,7 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>08-Jul-2025 (Tue)</t>
+          <t>09-Jul-2025 (Wed)</t>
         </is>
       </c>
       <c r="G42" s="15" t="n">
@@ -34884,7 +34884,7 @@
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>18-Jul-2025 (Fri)</t>
+          <t>17-Jul-2025 (Thu)</t>
         </is>
       </c>
       <c r="J42" s="15" t="n">
@@ -34945,7 +34945,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>31-Jul-2025 (Thu)</t>
+          <t>07-Aug-2025 (Thu)</t>
         </is>
       </c>
       <c r="G43" s="15" t="n">
@@ -34958,7 +34958,7 @@
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>13-Aug-2025 (Wed)</t>
+          <t>18-Aug-2025 (Mon)</t>
         </is>
       </c>
       <c r="J43" s="15" t="n">
@@ -35032,7 +35032,7 @@
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>15-Sep-2025 (Mon)</t>
+          <t>18-Sep-2025 (Thu)</t>
         </is>
       </c>
       <c r="J44" s="15" t="n">
@@ -35093,7 +35093,7 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>05-Sep-2025 (Fri)</t>
+          <t>11-Sep-2025 (Thu)</t>
         </is>
       </c>
       <c r="G45" s="15" t="n">
@@ -35241,7 +35241,7 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>11-Sep-2025 (Thu)</t>
+          <t>16-Sep-2025 (Tue)</t>
         </is>
       </c>
       <c r="G47" s="15" t="n">
@@ -35254,7 +35254,7 @@
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>23-Sep-2025 (Tue)</t>
+          <t>24-Sep-2025 (Wed)</t>
         </is>
       </c>
       <c r="J47" s="15" t="n">
@@ -35315,7 +35315,7 @@
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>10-Jul-2025 (Thu)</t>
+          <t>14-Jul-2025 (Mon)</t>
         </is>
       </c>
       <c r="G48" s="15" t="n">
@@ -35328,7 +35328,7 @@
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>18-Jul-2025 (Fri)</t>
+          <t>22-Jul-2025 (Tue)</t>
         </is>
       </c>
       <c r="J48" s="15" t="n">
@@ -35463,7 +35463,7 @@
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>05-Aug-2025 (Tue)</t>
+          <t>07-Aug-2025 (Thu)</t>
         </is>
       </c>
       <c r="G50" s="15" t="n">
@@ -35476,7 +35476,7 @@
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>13-Aug-2025 (Wed)</t>
+          <t>18-Aug-2025 (Mon)</t>
         </is>
       </c>
       <c r="J50" s="15" t="n">
@@ -35537,7 +35537,7 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>05-Sep-2025 (Fri)</t>
+          <t>11-Sep-2025 (Thu)</t>
         </is>
       </c>
       <c r="G51" s="15" t="n">
@@ -35550,7 +35550,7 @@
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>17-Sep-2025 (Wed)</t>
+          <t>19-Sep-2025 (Fri)</t>
         </is>
       </c>
       <c r="J51" s="15" t="n">
@@ -35611,7 +35611,7 @@
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>31-Jul-2025 (Thu)</t>
+          <t>07-Aug-2025 (Thu)</t>
         </is>
       </c>
       <c r="G52" s="15" t="n">
@@ -35624,7 +35624,7 @@
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>13-Aug-2025 (Wed)</t>
+          <t>18-Aug-2025 (Mon)</t>
         </is>
       </c>
       <c r="J52" s="15" t="n">
@@ -35685,7 +35685,7 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>11-Jul-2025 (Fri)</t>
+          <t>18-Jul-2025 (Fri)</t>
         </is>
       </c>
       <c r="G53" s="15" t="n">
@@ -35698,7 +35698,7 @@
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>29-Jul-2025 (Tue)</t>
+          <t>28-Jul-2025 (Mon)</t>
         </is>
       </c>
       <c r="J53" s="15" t="n">
@@ -35978,7 +35978,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>04-Apr-2025 (Fri)</t>
+          <t>08-Apr-2025 (Tue)</t>
         </is>
       </c>
       <c r="G5" s="15" t="n">
@@ -35991,7 +35991,7 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>17-Apr-2025 (Thu)</t>
+          <t>21-Apr-2025 (Mon)</t>
         </is>
       </c>
       <c r="J5" s="15" t="n">
@@ -36052,7 +36052,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>12-Jun-2025 (Thu)</t>
+          <t>16-Jun-2025 (Mon)</t>
         </is>
       </c>
       <c r="G6" s="15" t="n">
@@ -36065,7 +36065,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>23-Jun-2025 (Mon)</t>
+          <t>24-Jun-2025 (Tue)</t>
         </is>
       </c>
       <c r="J6" s="15" t="n">
@@ -36274,7 +36274,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>09-May-2025 (Fri)</t>
+          <t>16-May-2025 (Fri)</t>
         </is>
       </c>
       <c r="G9" s="15" t="n">
@@ -36287,7 +36287,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>27-May-2025 (Tue)</t>
+          <t>26-May-2025 (Mon)</t>
         </is>
       </c>
       <c r="J9" s="15" t="n">
@@ -36348,7 +36348,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>05-Jun-2025 (Thu)</t>
+          <t>10-Jun-2025 (Tue)</t>
         </is>
       </c>
       <c r="G10" s="15" t="n">
@@ -36361,7 +36361,7 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>16-Jun-2025 (Mon)</t>
+          <t>18-Jun-2025 (Wed)</t>
         </is>
       </c>
       <c r="J10" s="15" t="n">
@@ -36422,7 +36422,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>18-Jun-2025 (Wed)</t>
+          <t>20-Jun-2025 (Fri)</t>
         </is>
       </c>
       <c r="G11" s="15" t="n">
@@ -36435,7 +36435,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>26-Jun-2025 (Thu)</t>
+          <t>30-Jun-2025 (Mon)</t>
         </is>
       </c>
       <c r="J11" s="15" t="n">
@@ -36496,7 +36496,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>06-Jun-2025 (Fri)</t>
+          <t>10-Jun-2025 (Tue)</t>
         </is>
       </c>
       <c r="G12" s="15" t="n">
@@ -36509,7 +36509,7 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>19-Jun-2025 (Thu)</t>
+          <t>18-Jun-2025 (Wed)</t>
         </is>
       </c>
       <c r="J12" s="15" t="n">
@@ -36644,7 +36644,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>15-Apr-2025 (Tue)</t>
+          <t>17-Apr-2025 (Thu)</t>
         </is>
       </c>
       <c r="G14" s="15" t="n">
@@ -36657,7 +36657,7 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>29-Apr-2025 (Tue)</t>
+          <t>28-Apr-2025 (Mon)</t>
         </is>
       </c>
       <c r="J14" s="15" t="n">
@@ -36718,7 +36718,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>10-Jun-2025 (Tue)</t>
+          <t>16-Jun-2025 (Mon)</t>
         </is>
       </c>
       <c r="G15" s="15" t="n">
@@ -36731,7 +36731,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>20-Jun-2025 (Fri)</t>
+          <t>24-Jun-2025 (Tue)</t>
         </is>
       </c>
       <c r="J15" s="15" t="n">
@@ -36792,7 +36792,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>15-May-2025 (Thu)</t>
+          <t>21-May-2025 (Wed)</t>
         </is>
       </c>
       <c r="G16" s="15" t="n">
@@ -36866,7 +36866,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>04-Jun-2025 (Wed)</t>
+          <t>10-Jun-2025 (Tue)</t>
         </is>
       </c>
       <c r="G17" s="15" t="n">
@@ -36879,7 +36879,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>17-Jun-2025 (Tue)</t>
+          <t>18-Jun-2025 (Wed)</t>
         </is>
       </c>
       <c r="J17" s="15" t="n">
@@ -36940,7 +36940,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>04-Apr-2025 (Fri)</t>
+          <t>08-Apr-2025 (Tue)</t>
         </is>
       </c>
       <c r="G18" s="15" t="n">
@@ -36953,7 +36953,7 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>15-Apr-2025 (Tue)</t>
+          <t>21-Apr-2025 (Mon)</t>
         </is>
       </c>
       <c r="J18" s="15" t="n">
@@ -37014,7 +37014,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>13-May-2025 (Tue)</t>
+          <t>14-May-2025 (Wed)</t>
         </is>
       </c>
       <c r="G19" s="15" t="n">
@@ -37027,7 +37027,7 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>20-May-2025 (Tue)</t>
+          <t>22-May-2025 (Thu)</t>
         </is>
       </c>
       <c r="J19" s="15" t="n">
@@ -37088,7 +37088,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>02-Apr-2025 (Wed)</t>
+          <t>08-Apr-2025 (Tue)</t>
         </is>
       </c>
       <c r="G20" s="15" t="n">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>16-Apr-2025 (Wed)</t>
+          <t>21-Apr-2025 (Mon)</t>
         </is>
       </c>
       <c r="J20" s="15" t="n">
@@ -37162,7 +37162,7 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>11-Apr-2025 (Fri)</t>
+          <t>17-Apr-2025 (Thu)</t>
         </is>
       </c>
       <c r="G21" s="15" t="n">
@@ -37175,7 +37175,7 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>24-Apr-2025 (Thu)</t>
+          <t>28-Apr-2025 (Mon)</t>
         </is>
       </c>
       <c r="J21" s="15" t="n">
@@ -37310,7 +37310,7 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>04-Jun-2025 (Wed)</t>
+          <t>11-Jun-2025 (Wed)</t>
         </is>
       </c>
       <c r="G23" s="15" t="n">
@@ -37323,7 +37323,7 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>20-Jun-2025 (Fri)</t>
+          <t>19-Jun-2025 (Thu)</t>
         </is>
       </c>
       <c r="J23" s="15" t="n">
@@ -37384,7 +37384,7 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>15-Apr-2025 (Tue)</t>
+          <t>17-Apr-2025 (Thu)</t>
         </is>
       </c>
       <c r="G24" s="15" t="n">
@@ -37397,7 +37397,7 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>29-Apr-2025 (Tue)</t>
+          <t>28-Apr-2025 (Mon)</t>
         </is>
       </c>
       <c r="J24" s="15" t="n">
@@ -37532,7 +37532,7 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>06-Jun-2025 (Fri)</t>
+          <t>11-Jun-2025 (Wed)</t>
         </is>
       </c>
       <c r="G26" s="15" t="n">
@@ -37606,7 +37606,7 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>13-May-2025 (Tue)</t>
+          <t>16-May-2025 (Fri)</t>
         </is>
       </c>
       <c r="G27" s="15" t="n">
@@ -37680,7 +37680,7 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>06-May-2025 (Tue)</t>
+          <t>07-May-2025 (Wed)</t>
         </is>
       </c>
       <c r="G28" s="15" t="n">
@@ -37693,7 +37693,7 @@
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>14-May-2025 (Wed)</t>
+          <t>15-May-2025 (Thu)</t>
         </is>
       </c>
       <c r="J28" s="15" t="n">
@@ -37754,7 +37754,7 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>15-May-2025 (Thu)</t>
+          <t>21-May-2025 (Wed)</t>
         </is>
       </c>
       <c r="G29" s="15" t="n">
@@ -37767,7 +37767,7 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>27-May-2025 (Tue)</t>
+          <t>29-May-2025 (Thu)</t>
         </is>
       </c>
       <c r="J29" s="15" t="n">
@@ -37976,7 +37976,7 @@
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>17-Jun-2025 (Tue)</t>
+          <t>18-Jun-2025 (Wed)</t>
         </is>
       </c>
       <c r="G32" s="15" t="n">
@@ -37989,7 +37989,7 @@
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>23-Jun-2025 (Mon)</t>
+          <t>26-Jun-2025 (Thu)</t>
         </is>
       </c>
       <c r="J32" s="15" t="n">
@@ -38050,7 +38050,7 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>28-Mar-2025 (Fri)</t>
+          <t>07-Apr-2025 (Mon)</t>
         </is>
       </c>
       <c r="G33" s="15" t="n">
@@ -38063,7 +38063,7 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>21-Apr-2025 (Mon)</t>
+          <t>17-Apr-2025 (Thu)</t>
         </is>
       </c>
       <c r="J33" s="15" t="n">
@@ -38124,7 +38124,7 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>08-May-2025 (Thu)</t>
+          <t>14-May-2025 (Wed)</t>
         </is>
       </c>
       <c r="G34" s="15" t="n">
@@ -38137,7 +38137,7 @@
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>21-May-2025 (Wed)</t>
+          <t>22-May-2025 (Thu)</t>
         </is>
       </c>
       <c r="J34" s="15" t="n">
@@ -38198,7 +38198,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>12-Jun-2025 (Thu)</t>
+          <t>16-Jun-2025 (Mon)</t>
         </is>
       </c>
       <c r="G35" s="15" t="n">
@@ -38211,7 +38211,7 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>19-Jun-2025 (Thu)</t>
+          <t>24-Jun-2025 (Tue)</t>
         </is>
       </c>
       <c r="J35" s="15" t="n">
@@ -38272,7 +38272,7 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>10-Jun-2025 (Tue)</t>
+          <t>16-Jun-2025 (Mon)</t>
         </is>
       </c>
       <c r="G36" s="15" t="n">
@@ -38346,7 +38346,7 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>10-Jun-2025 (Tue)</t>
+          <t>16-Jun-2025 (Mon)</t>
         </is>
       </c>
       <c r="G37" s="15" t="n">
@@ -38359,7 +38359,7 @@
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>20-Jun-2025 (Fri)</t>
+          <t>24-Jun-2025 (Tue)</t>
         </is>
       </c>
       <c r="J37" s="15" t="n">
@@ -38420,7 +38420,7 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>13-May-2025 (Tue)</t>
+          <t>16-May-2025 (Fri)</t>
         </is>
       </c>
       <c r="G38" s="15" t="n">
@@ -38568,7 +38568,7 @@
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>09-Apr-2025 (Wed)</t>
+          <t>11-Apr-2025 (Fri)</t>
         </is>
       </c>
       <c r="G40" s="15" t="n">
@@ -38581,7 +38581,7 @@
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>22-Apr-2025 (Tue)</t>
+          <t>23-Apr-2025 (Wed)</t>
         </is>
       </c>
       <c r="J40" s="15" t="n">
@@ -38642,7 +38642,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>09-Jun-2025 (Mon)</t>
+          <t>10-Jun-2025 (Tue)</t>
         </is>
       </c>
       <c r="G41" s="15" t="n">
@@ -38655,7 +38655,7 @@
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>16-Jun-2025 (Mon)</t>
+          <t>18-Jun-2025 (Wed)</t>
         </is>
       </c>
       <c r="J41" s="15" t="n">
@@ -38716,7 +38716,7 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>09-Jun-2025 (Mon)</t>
+          <t>10-Jun-2025 (Tue)</t>
         </is>
       </c>
       <c r="G42" s="15" t="n">
@@ -38729,7 +38729,7 @@
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>16-Jun-2025 (Mon)</t>
+          <t>18-Jun-2025 (Wed)</t>
         </is>
       </c>
       <c r="J42" s="15" t="n">
@@ -38790,7 +38790,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>07-Apr-2025 (Mon)</t>
+          <t>11-Apr-2025 (Fri)</t>
         </is>
       </c>
       <c r="G43" s="15" t="n">
@@ -38803,7 +38803,7 @@
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>22-Apr-2025 (Tue)</t>
+          <t>23-Apr-2025 (Wed)</t>
         </is>
       </c>
       <c r="J43" s="15" t="n">
@@ -38864,7 +38864,7 @@
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>07-May-2025 (Wed)</t>
+          <t>12-May-2025 (Mon)</t>
         </is>
       </c>
       <c r="G44" s="15" t="n">
@@ -38877,7 +38877,7 @@
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>21-May-2025 (Wed)</t>
+          <t>20-May-2025 (Tue)</t>
         </is>
       </c>
       <c r="J44" s="15" t="n">
@@ -38951,7 +38951,7 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>16-Jun-2025 (Mon)</t>
+          <t>19-Jun-2025 (Thu)</t>
         </is>
       </c>
       <c r="J45" s="15" t="n">
@@ -39012,7 +39012,7 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>02-Apr-2025 (Wed)</t>
+          <t>08-Apr-2025 (Tue)</t>
         </is>
       </c>
       <c r="G46" s="15" t="n">
@@ -39025,7 +39025,7 @@
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>16-Apr-2025 (Wed)</t>
+          <t>21-Apr-2025 (Mon)</t>
         </is>
       </c>
       <c r="J46" s="15" t="n">
@@ -39086,7 +39086,7 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>06-May-2025 (Tue)</t>
+          <t>07-May-2025 (Wed)</t>
         </is>
       </c>
       <c r="G47" s="15" t="n">
@@ -39099,7 +39099,7 @@
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>12-May-2025 (Mon)</t>
+          <t>15-May-2025 (Thu)</t>
         </is>
       </c>
       <c r="J47" s="15" t="n">
@@ -39160,7 +39160,7 @@
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>12-May-2025 (Mon)</t>
+          <t>14-May-2025 (Wed)</t>
         </is>
       </c>
       <c r="G48" s="15" t="n">
@@ -39173,7 +39173,7 @@
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>23-May-2025 (Fri)</t>
+          <t>22-May-2025 (Thu)</t>
         </is>
       </c>
       <c r="J48" s="15" t="n">
@@ -39234,7 +39234,7 @@
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>02-May-2025 (Fri)</t>
+          <t>07-May-2025 (Wed)</t>
         </is>
       </c>
       <c r="G49" s="15" t="n">
@@ -39247,7 +39247,7 @@
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>14-May-2025 (Wed)</t>
+          <t>15-May-2025 (Thu)</t>
         </is>
       </c>
       <c r="J49" s="15" t="n">
@@ -39321,7 +39321,7 @@
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>11-Apr-2025 (Fri)</t>
+          <t>17-Apr-2025 (Thu)</t>
         </is>
       </c>
       <c r="J50" s="15" t="n">
@@ -39456,7 +39456,7 @@
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>06-May-2025 (Tue)</t>
+          <t>07-May-2025 (Wed)</t>
         </is>
       </c>
       <c r="G52" s="15" t="n">
@@ -39469,7 +39469,7 @@
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>12-May-2025 (Mon)</t>
+          <t>15-May-2025 (Thu)</t>
         </is>
       </c>
       <c r="J52" s="15" t="n">
@@ -39530,7 +39530,7 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>15-Apr-2025 (Tue)</t>
+          <t>17-Apr-2025 (Thu)</t>
         </is>
       </c>
       <c r="G53" s="15" t="n">
@@ -39543,7 +39543,7 @@
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>29-Apr-2025 (Tue)</t>
+          <t>28-Apr-2025 (Mon)</t>
         </is>
       </c>
       <c r="J53" s="15" t="n">
@@ -39604,7 +39604,7 @@
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>07-Apr-2025 (Mon)</t>
+          <t>11-Apr-2025 (Fri)</t>
         </is>
       </c>
       <c r="G54" s="15" t="n">
@@ -39617,7 +39617,7 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>22-Apr-2025 (Tue)</t>
+          <t>23-Apr-2025 (Wed)</t>
         </is>
       </c>
       <c r="J54" s="15" t="n">
@@ -39823,7 +39823,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>06-Jan-2025 (Mon)</t>
+          <t>09-Jan-2025 (Thu)</t>
         </is>
       </c>
       <c r="G5" s="15" t="n">
@@ -39910,7 +39910,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>20-Mar-2025 (Thu)</t>
+          <t>19-Mar-2025 (Wed)</t>
         </is>
       </c>
       <c r="J6" s="15" t="n">
@@ -39971,7 +39971,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>14-Feb-2025 (Fri)</t>
+          <t>18-Feb-2025 (Tue)</t>
         </is>
       </c>
       <c r="G7" s="15" t="n">
@@ -39984,7 +39984,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>28-Feb-2025 (Fri)</t>
+          <t>26-Feb-2025 (Wed)</t>
         </is>
       </c>
       <c r="J7" s="15" t="n">
@@ -40045,7 +40045,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>15-Jan-2025 (Wed)</t>
+          <t>20-Jan-2025 (Mon)</t>
         </is>
       </c>
       <c r="G8" s="15" t="n">
@@ -40058,7 +40058,7 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>29-Jan-2025 (Wed)</t>
+          <t>28-Jan-2025 (Tue)</t>
         </is>
       </c>
       <c r="J8" s="15" t="n">
@@ -40119,7 +40119,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>05-Mar-2025 (Wed)</t>
+          <t>10-Mar-2025 (Mon)</t>
         </is>
       </c>
       <c r="G9" s="15" t="n">
@@ -40132,7 +40132,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>20-Mar-2025 (Thu)</t>
+          <t>19-Mar-2025 (Wed)</t>
         </is>
       </c>
       <c r="J9" s="15" t="n">
@@ -40193,7 +40193,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>12-Feb-2025 (Wed)</t>
+          <t>19-Feb-2025 (Wed)</t>
         </is>
       </c>
       <c r="G10" s="15" t="n">
@@ -40206,7 +40206,7 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>03-Mar-2025 (Mon)</t>
+          <t>27-Feb-2025 (Thu)</t>
         </is>
       </c>
       <c r="J10" s="15" t="n">
@@ -40267,7 +40267,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>05-Feb-2025 (Wed)</t>
+          <t>07-Feb-2025 (Fri)</t>
         </is>
       </c>
       <c r="G11" s="15" t="n">
@@ -40280,7 +40280,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>14-Feb-2025 (Fri)</t>
+          <t>17-Feb-2025 (Mon)</t>
         </is>
       </c>
       <c r="J11" s="15" t="n">
@@ -40341,7 +40341,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>03-Jan-2025 (Fri)</t>
+          <t>08-Jan-2025 (Wed)</t>
         </is>
       </c>
       <c r="G12" s="15" t="n">
@@ -40354,7 +40354,7 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>14-Jan-2025 (Tue)</t>
+          <t>16-Jan-2025 (Thu)</t>
         </is>
       </c>
       <c r="J12" s="15" t="n">
@@ -40415,7 +40415,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>10-Mar-2025 (Mon)</t>
+          <t>13-Mar-2025 (Thu)</t>
         </is>
       </c>
       <c r="G13" s="15" t="n">
@@ -40489,7 +40489,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>11-Feb-2025 (Tue)</t>
+          <t>13-Feb-2025 (Thu)</t>
         </is>
       </c>
       <c r="G14" s="15" t="n">
@@ -40502,7 +40502,7 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>19-Feb-2025 (Wed)</t>
+          <t>21-Feb-2025 (Fri)</t>
         </is>
       </c>
       <c r="J14" s="15" t="n">
@@ -40563,7 +40563,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>17-Mar-2025 (Mon)</t>
+          <t>20-Mar-2025 (Thu)</t>
         </is>
       </c>
       <c r="G15" s="15" t="n">
@@ -40576,7 +40576,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>27-Mar-2025 (Thu)</t>
+          <t>28-Mar-2025 (Fri)</t>
         </is>
       </c>
       <c r="J15" s="15" t="n">
@@ -40637,7 +40637,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>06-Mar-2025 (Thu)</t>
+          <t>10-Mar-2025 (Mon)</t>
         </is>
       </c>
       <c r="G16" s="15" t="n">
@@ -40650,7 +40650,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>17-Mar-2025 (Mon)</t>
+          <t>19-Mar-2025 (Wed)</t>
         </is>
       </c>
       <c r="J16" s="15" t="n">
@@ -40859,7 +40859,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>11-Feb-2025 (Tue)</t>
+          <t>12-Feb-2025 (Wed)</t>
         </is>
       </c>
       <c r="G19" s="15" t="n">
@@ -40872,7 +40872,7 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>21-Feb-2025 (Fri)</t>
+          <t>20-Feb-2025 (Thu)</t>
         </is>
       </c>
       <c r="J19" s="15" t="n">
@@ -41020,7 +41020,7 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>14-Jan-2025 (Tue)</t>
+          <t>17-Jan-2025 (Fri)</t>
         </is>
       </c>
       <c r="J21" s="15" t="n">
@@ -41081,7 +41081,7 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>06-Mar-2025 (Thu)</t>
+          <t>11-Mar-2025 (Tue)</t>
         </is>
       </c>
       <c r="G22" s="15" t="n">
@@ -41094,7 +41094,7 @@
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>18-Mar-2025 (Tue)</t>
+          <t>20-Mar-2025 (Thu)</t>
         </is>
       </c>
       <c r="J22" s="15" t="n">
@@ -41242,7 +41242,7 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>29-Jan-2025 (Wed)</t>
+          <t>28-Jan-2025 (Tue)</t>
         </is>
       </c>
       <c r="J24" s="15" t="n">
@@ -41316,7 +41316,7 @@
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>28-Feb-2025 (Fri)</t>
+          <t>27-Feb-2025 (Thu)</t>
         </is>
       </c>
       <c r="J25" s="15" t="n">
@@ -41377,7 +41377,7 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>17-Mar-2025 (Mon)</t>
+          <t>19-Mar-2025 (Wed)</t>
         </is>
       </c>
       <c r="G26" s="15" t="n">
@@ -41390,7 +41390,7 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>24-Mar-2025 (Mon)</t>
+          <t>27-Mar-2025 (Thu)</t>
         </is>
       </c>
       <c r="J26" s="15" t="n">
@@ -41525,7 +41525,7 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>03-Mar-2025 (Mon)</t>
+          <t>10-Mar-2025 (Mon)</t>
         </is>
       </c>
       <c r="G28" s="15" t="n">
@@ -41538,7 +41538,7 @@
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>17-Mar-2025 (Mon)</t>
+          <t>19-Mar-2025 (Wed)</t>
         </is>
       </c>
       <c r="J28" s="15" t="n">
@@ -41599,7 +41599,7 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>15-Jan-2025 (Wed)</t>
+          <t>20-Jan-2025 (Mon)</t>
         </is>
       </c>
       <c r="G29" s="15" t="n">
@@ -41612,7 +41612,7 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>29-Jan-2025 (Wed)</t>
+          <t>28-Jan-2025 (Tue)</t>
         </is>
       </c>
       <c r="J29" s="15" t="n">
@@ -41673,7 +41673,7 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>07-Jan-2025 (Tue)</t>
+          <t>08-Jan-2025 (Wed)</t>
         </is>
       </c>
       <c r="G30" s="15" t="n">
@@ -41686,7 +41686,7 @@
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>14-Jan-2025 (Tue)</t>
+          <t>16-Jan-2025 (Thu)</t>
         </is>
       </c>
       <c r="J30" s="15" t="n">
@@ -41760,7 +41760,7 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>19-Mar-2025 (Wed)</t>
+          <t>24-Mar-2025 (Mon)</t>
         </is>
       </c>
       <c r="J31" s="15" t="n">
@@ -41821,7 +41821,7 @@
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>07-Mar-2025 (Fri)</t>
+          <t>11-Mar-2025 (Tue)</t>
         </is>
       </c>
       <c r="G32" s="15" t="n">
@@ -41834,7 +41834,7 @@
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>21-Mar-2025 (Fri)</t>
+          <t>20-Mar-2025 (Thu)</t>
         </is>
       </c>
       <c r="J32" s="15" t="n">
@@ -41895,7 +41895,7 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>06-Jan-2025 (Mon)</t>
+          <t>08-Jan-2025 (Wed)</t>
         </is>
       </c>
       <c r="G33" s="15" t="n">
@@ -41908,7 +41908,7 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>17-Jan-2025 (Fri)</t>
+          <t>16-Jan-2025 (Thu)</t>
         </is>
       </c>
       <c r="J33" s="15" t="n">
@@ -41969,7 +41969,7 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>06-Mar-2025 (Thu)</t>
+          <t>10-Mar-2025 (Mon)</t>
         </is>
       </c>
       <c r="G34" s="15" t="n">
@@ -41982,7 +41982,7 @@
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>17-Mar-2025 (Mon)</t>
+          <t>19-Mar-2025 (Wed)</t>
         </is>
       </c>
       <c r="J34" s="15" t="n">
@@ -42043,7 +42043,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>10-Mar-2025 (Mon)</t>
+          <t>11-Mar-2025 (Tue)</t>
         </is>
       </c>
       <c r="G35" s="15" t="n">
@@ -42056,7 +42056,7 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>18-Mar-2025 (Tue)</t>
+          <t>20-Mar-2025 (Thu)</t>
         </is>
       </c>
       <c r="J35" s="15" t="n">
@@ -42117,7 +42117,7 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>06-Feb-2025 (Thu)</t>
+          <t>13-Feb-2025 (Thu)</t>
         </is>
       </c>
       <c r="G36" s="15" t="n">
@@ -42130,7 +42130,7 @@
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>19-Feb-2025 (Wed)</t>
+          <t>21-Feb-2025 (Fri)</t>
         </is>
       </c>
       <c r="J36" s="15" t="n">
@@ -42191,7 +42191,7 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>05-Feb-2025 (Wed)</t>
+          <t>07-Feb-2025 (Fri)</t>
         </is>
       </c>
       <c r="G37" s="15" t="n">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>12-Feb-2025 (Wed)</t>
+          <t>17-Feb-2025 (Mon)</t>
         </is>
       </c>
       <c r="J37" s="15" t="n">
@@ -42265,7 +42265,7 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>10-Jan-2025 (Fri)</t>
+          <t>14-Jan-2025 (Tue)</t>
         </is>
       </c>
       <c r="G38" s="15" t="n">
@@ -42278,7 +42278,7 @@
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>21-Jan-2025 (Tue)</t>
+          <t>22-Jan-2025 (Wed)</t>
         </is>
       </c>
       <c r="J38" s="15" t="n">
@@ -42339,7 +42339,7 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>03-Feb-2025 (Mon)</t>
+          <t>07-Feb-2025 (Fri)</t>
         </is>
       </c>
       <c r="G39" s="15" t="n">
@@ -42561,7 +42561,7 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>10-Feb-2025 (Mon)</t>
+          <t>13-Feb-2025 (Thu)</t>
         </is>
       </c>
       <c r="G42" s="15" t="n">
@@ -42574,7 +42574,7 @@
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>24-Feb-2025 (Mon)</t>
+          <t>21-Feb-2025 (Fri)</t>
         </is>
       </c>
       <c r="J42" s="15" t="n">
@@ -42783,7 +42783,7 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>08-Jan-2025 (Wed)</t>
+          <t>14-Jan-2025 (Tue)</t>
         </is>
       </c>
       <c r="G45" s="15" t="n">
@@ -42857,7 +42857,7 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>12-Feb-2025 (Wed)</t>
+          <t>18-Feb-2025 (Tue)</t>
         </is>
       </c>
       <c r="G46" s="15" t="n">
@@ -42870,7 +42870,7 @@
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>25-Feb-2025 (Tue)</t>
+          <t>26-Feb-2025 (Wed)</t>
         </is>
       </c>
       <c r="J46" s="15" t="n">
@@ -42931,7 +42931,7 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>05-Feb-2025 (Wed)</t>
+          <t>07-Feb-2025 (Fri)</t>
         </is>
       </c>
       <c r="G47" s="15" t="n">
@@ -42944,7 +42944,7 @@
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>12-Feb-2025 (Wed)</t>
+          <t>17-Feb-2025 (Mon)</t>
         </is>
       </c>
       <c r="J47" s="15" t="n">
@@ -43005,7 +43005,7 @@
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>08-Jan-2025 (Wed)</t>
+          <t>14-Jan-2025 (Tue)</t>
         </is>
       </c>
       <c r="G48" s="15" t="n">
@@ -43153,7 +43153,7 @@
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>05-Mar-2025 (Wed)</t>
+          <t>11-Mar-2025 (Tue)</t>
         </is>
       </c>
       <c r="G50" s="15" t="n">
@@ -43166,7 +43166,7 @@
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>19-Mar-2025 (Wed)</t>
+          <t>20-Mar-2025 (Thu)</t>
         </is>
       </c>
       <c r="J50" s="15" t="n">
@@ -43227,7 +43227,7 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>15-Jan-2025 (Wed)</t>
+          <t>20-Jan-2025 (Mon)</t>
         </is>
       </c>
       <c r="G51" s="15" t="n">
@@ -43240,7 +43240,7 @@
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>29-Jan-2025 (Wed)</t>
+          <t>28-Jan-2025 (Tue)</t>
         </is>
       </c>
       <c r="J51" s="15" t="n">
@@ -43301,7 +43301,7 @@
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>12-Feb-2025 (Wed)</t>
+          <t>18-Feb-2025 (Tue)</t>
         </is>
       </c>
       <c r="G52" s="15" t="n">
@@ -43314,7 +43314,7 @@
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>25-Feb-2025 (Tue)</t>
+          <t>26-Feb-2025 (Wed)</t>
         </is>
       </c>
       <c r="J52" s="15" t="n">
@@ -43375,7 +43375,7 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>06-Mar-2025 (Thu)</t>
+          <t>13-Mar-2025 (Thu)</t>
         </is>
       </c>
       <c r="G53" s="15" t="n">
@@ -43388,7 +43388,7 @@
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>25-Mar-2025 (Tue)</t>
+          <t>24-Mar-2025 (Mon)</t>
         </is>
       </c>
       <c r="J53" s="15" t="n">
@@ -43449,7 +43449,7 @@
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>06-Mar-2025 (Thu)</t>
+          <t>11-Mar-2025 (Tue)</t>
         </is>
       </c>
       <c r="G54" s="15" t="n">
@@ -43462,7 +43462,7 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>18-Mar-2025 (Tue)</t>
+          <t>20-Mar-2025 (Thu)</t>
         </is>
       </c>
       <c r="J54" s="15" t="n">
@@ -43668,7 +43668,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>03-Oct-2024 (Thu)</t>
+          <t>09-Oct-2024 (Wed)</t>
         </is>
       </c>
       <c r="G5" s="15" t="n">
@@ -43681,7 +43681,7 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>16-Oct-2024 (Wed)</t>
+          <t>17-Oct-2024 (Thu)</t>
         </is>
       </c>
       <c r="J5" s="15" t="n">
@@ -43742,7 +43742,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>09-Dec-2024 (Mon)</t>
+          <t>10-Dec-2024 (Tue)</t>
         </is>
       </c>
       <c r="G6" s="15" t="n">
@@ -43755,7 +43755,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>17-Dec-2024 (Tue)</t>
+          <t>18-Dec-2024 (Wed)</t>
         </is>
       </c>
       <c r="J6" s="15" t="n">
@@ -43816,7 +43816,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>10-Dec-2024 (Tue)</t>
+          <t>16-Dec-2024 (Mon)</t>
         </is>
       </c>
       <c r="G7" s="15" t="n">
@@ -43829,7 +43829,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>23-Dec-2024 (Mon)</t>
+          <t>24-Dec-2024 (Tue)</t>
         </is>
       </c>
       <c r="J7" s="15" t="n">
@@ -43903,7 +43903,7 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>17-Oct-2024 (Thu)</t>
+          <t>16-Oct-2024 (Wed)</t>
         </is>
       </c>
       <c r="J8" s="15" t="n">
@@ -43964,7 +43964,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>09-Dec-2024 (Mon)</t>
+          <t>10-Dec-2024 (Tue)</t>
         </is>
       </c>
       <c r="G9" s="15" t="n">
@@ -43977,7 +43977,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>19-Dec-2024 (Thu)</t>
+          <t>18-Dec-2024 (Wed)</t>
         </is>
       </c>
       <c r="J9" s="15" t="n">
@@ -44038,7 +44038,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>17-Oct-2024 (Thu)</t>
+          <t>18-Oct-2024 (Fri)</t>
         </is>
       </c>
       <c r="G10" s="15" t="n">
@@ -44051,7 +44051,7 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>29-Oct-2024 (Tue)</t>
+          <t>28-Oct-2024 (Mon)</t>
         </is>
       </c>
       <c r="J10" s="15" t="n">
@@ -44112,7 +44112,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>12-Nov-2024 (Tue)</t>
+          <t>18-Nov-2024 (Mon)</t>
         </is>
       </c>
       <c r="G11" s="15" t="n">
@@ -44125,7 +44125,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>27-Nov-2024 (Wed)</t>
+          <t>26-Nov-2024 (Tue)</t>
         </is>
       </c>
       <c r="J11" s="15" t="n">
@@ -44260,7 +44260,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>04-Nov-2024 (Mon)</t>
+          <t>07-Nov-2024 (Thu)</t>
         </is>
       </c>
       <c r="G13" s="15" t="n">
@@ -44347,7 +44347,7 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>20-Dec-2024 (Fri)</t>
+          <t>19-Dec-2024 (Thu)</t>
         </is>
       </c>
       <c r="J14" s="15" t="n">
@@ -44408,7 +44408,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>06-Dec-2024 (Fri)</t>
+          <t>11-Dec-2024 (Wed)</t>
         </is>
       </c>
       <c r="G15" s="15" t="n">
@@ -44421,7 +44421,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>20-Dec-2024 (Fri)</t>
+          <t>19-Dec-2024 (Thu)</t>
         </is>
       </c>
       <c r="J15" s="15" t="n">
@@ -44482,7 +44482,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>08-Oct-2024 (Tue)</t>
+          <t>09-Oct-2024 (Wed)</t>
         </is>
       </c>
       <c r="G16" s="15" t="n">
@@ -44495,7 +44495,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>15-Oct-2024 (Tue)</t>
+          <t>17-Oct-2024 (Thu)</t>
         </is>
       </c>
       <c r="J16" s="15" t="n">
@@ -44556,7 +44556,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>11-Dec-2024 (Wed)</t>
+          <t>16-Dec-2024 (Mon)</t>
         </is>
       </c>
       <c r="G17" s="15" t="n">
@@ -44569,7 +44569,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>20-Dec-2024 (Fri)</t>
+          <t>24-Dec-2024 (Tue)</t>
         </is>
       </c>
       <c r="J17" s="15" t="n">
@@ -44630,7 +44630,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>16-Dec-2024 (Mon)</t>
+          <t>20-Dec-2024 (Fri)</t>
         </is>
       </c>
       <c r="G18" s="15" t="n">
@@ -44704,7 +44704,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>04-Oct-2024 (Fri)</t>
+          <t>09-Oct-2024 (Wed)</t>
         </is>
       </c>
       <c r="G19" s="15" t="n">
@@ -44717,7 +44717,7 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>15-Oct-2024 (Tue)</t>
+          <t>17-Oct-2024 (Thu)</t>
         </is>
       </c>
       <c r="J19" s="15" t="n">
@@ -44852,7 +44852,7 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>04-Dec-2024 (Wed)</t>
+          <t>11-Dec-2024 (Wed)</t>
         </is>
       </c>
       <c r="G21" s="15" t="n">
@@ -44865,7 +44865,7 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>17-Dec-2024 (Tue)</t>
+          <t>19-Dec-2024 (Thu)</t>
         </is>
       </c>
       <c r="J21" s="15" t="n">
@@ -45000,7 +45000,7 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>09-Dec-2024 (Mon)</t>
+          <t>11-Dec-2024 (Wed)</t>
         </is>
       </c>
       <c r="G23" s="15" t="n">
@@ -45013,7 +45013,7 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>17-Dec-2024 (Tue)</t>
+          <t>19-Dec-2024 (Thu)</t>
         </is>
       </c>
       <c r="J23" s="15" t="n">
@@ -45074,7 +45074,7 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>18-Nov-2024 (Mon)</t>
+          <t>20-Nov-2024 (Wed)</t>
         </is>
       </c>
       <c r="G24" s="15" t="n">
@@ -45087,7 +45087,7 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>29-Nov-2024 (Fri)</t>
+          <t>28-Nov-2024 (Thu)</t>
         </is>
       </c>
       <c r="J24" s="15" t="n">
@@ -45148,7 +45148,7 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>06-Nov-2024 (Wed)</t>
+          <t>12-Nov-2024 (Tue)</t>
         </is>
       </c>
       <c r="G25" s="15" t="n">
@@ -45161,7 +45161,7 @@
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>19-Nov-2024 (Tue)</t>
+          <t>21-Nov-2024 (Thu)</t>
         </is>
       </c>
       <c r="J25" s="15" t="n">
@@ -45235,7 +45235,7 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>23-Dec-2024 (Mon)</t>
+          <t>27-Dec-2024 (Fri)</t>
         </is>
       </c>
       <c r="J26" s="15" t="n">
@@ -45296,7 +45296,7 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>17-Oct-2024 (Thu)</t>
+          <t>18-Oct-2024 (Fri)</t>
         </is>
       </c>
       <c r="G27" s="15" t="n">
@@ -45309,7 +45309,7 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>25-Oct-2024 (Fri)</t>
+          <t>28-Oct-2024 (Mon)</t>
         </is>
       </c>
       <c r="J27" s="15" t="n">
@@ -45370,7 +45370,7 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>05-Dec-2024 (Thu)</t>
+          <t>10-Dec-2024 (Tue)</t>
         </is>
       </c>
       <c r="G28" s="15" t="n">
@@ -45383,7 +45383,7 @@
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>17-Dec-2024 (Tue)</t>
+          <t>18-Dec-2024 (Wed)</t>
         </is>
       </c>
       <c r="J28" s="15" t="n">
@@ -45444,7 +45444,7 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>03-Oct-2024 (Thu)</t>
+          <t>08-Oct-2024 (Tue)</t>
         </is>
       </c>
       <c r="G29" s="15" t="n">
@@ -45457,7 +45457,7 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>17-Oct-2024 (Thu)</t>
+          <t>16-Oct-2024 (Wed)</t>
         </is>
       </c>
       <c r="J29" s="15" t="n">
@@ -45592,7 +45592,7 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>11-Dec-2024 (Wed)</t>
+          <t>16-Dec-2024 (Mon)</t>
         </is>
       </c>
       <c r="G31" s="15" t="n">
@@ -45605,7 +45605,7 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>20-Dec-2024 (Fri)</t>
+          <t>24-Dec-2024 (Tue)</t>
         </is>
       </c>
       <c r="J31" s="15" t="n">
@@ -45666,7 +45666,7 @@
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>11-Nov-2024 (Mon)</t>
+          <t>12-Nov-2024 (Tue)</t>
         </is>
       </c>
       <c r="G32" s="15" t="n">
@@ -45679,7 +45679,7 @@
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>18-Nov-2024 (Mon)</t>
+          <t>21-Nov-2024 (Thu)</t>
         </is>
       </c>
       <c r="J32" s="15" t="n">
@@ -45740,7 +45740,7 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>14-Nov-2024 (Thu)</t>
+          <t>20-Nov-2024 (Wed)</t>
         </is>
       </c>
       <c r="G33" s="15" t="n">
@@ -45753,7 +45753,7 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>26-Nov-2024 (Tue)</t>
+          <t>28-Nov-2024 (Thu)</t>
         </is>
       </c>
       <c r="J33" s="15" t="n">
@@ -45814,7 +45814,7 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>04-Oct-2024 (Fri)</t>
+          <t>08-Oct-2024 (Tue)</t>
         </is>
       </c>
       <c r="G34" s="15" t="n">
@@ -45827,7 +45827,7 @@
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>14-Oct-2024 (Mon)</t>
+          <t>16-Oct-2024 (Wed)</t>
         </is>
       </c>
       <c r="J34" s="15" t="n">
@@ -45888,7 +45888,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>13-Dec-2024 (Fri)</t>
+          <t>16-Dec-2024 (Mon)</t>
         </is>
       </c>
       <c r="G35" s="15" t="n">
@@ -45901,7 +45901,7 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>20-Dec-2024 (Fri)</t>
+          <t>24-Dec-2024 (Tue)</t>
         </is>
       </c>
       <c r="J35" s="15" t="n">
@@ -45962,7 +45962,7 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>07-Oct-2024 (Mon)</t>
+          <t>14-Oct-2024 (Mon)</t>
         </is>
       </c>
       <c r="G36" s="15" t="n">
@@ -45975,7 +45975,7 @@
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>23-Oct-2024 (Wed)</t>
+          <t>22-Oct-2024 (Tue)</t>
         </is>
       </c>
       <c r="J36" s="15" t="n">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>17-Oct-2024 (Thu)</t>
+          <t>18-Oct-2024 (Fri)</t>
         </is>
       </c>
       <c r="G38" s="15" t="n">
@@ -46123,7 +46123,7 @@
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>29-Oct-2024 (Tue)</t>
+          <t>28-Oct-2024 (Mon)</t>
         </is>
       </c>
       <c r="J38" s="15" t="n">
@@ -46197,7 +46197,7 @@
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>12-Nov-2024 (Tue)</t>
+          <t>18-Nov-2024 (Mon)</t>
         </is>
       </c>
       <c r="J39" s="15" t="n">
@@ -46258,7 +46258,7 @@
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>05-Dec-2024 (Thu)</t>
+          <t>10-Dec-2024 (Tue)</t>
         </is>
       </c>
       <c r="G40" s="15" t="n">
@@ -46271,7 +46271,7 @@
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>17-Dec-2024 (Tue)</t>
+          <t>18-Dec-2024 (Wed)</t>
         </is>
       </c>
       <c r="J40" s="15" t="n">
@@ -46332,7 +46332,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>08-Nov-2024 (Fri)</t>
+          <t>18-Nov-2024 (Mon)</t>
         </is>
       </c>
       <c r="G41" s="15" t="n">
@@ -46345,7 +46345,7 @@
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>22-Nov-2024 (Fri)</t>
+          <t>26-Nov-2024 (Tue)</t>
         </is>
       </c>
       <c r="J41" s="15" t="n">
@@ -46406,7 +46406,7 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>09-Dec-2024 (Mon)</t>
+          <t>10-Dec-2024 (Tue)</t>
         </is>
       </c>
       <c r="G42" s="15" t="n">
@@ -46419,7 +46419,7 @@
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>13-Dec-2024 (Fri)</t>
+          <t>18-Dec-2024 (Wed)</t>
         </is>
       </c>
       <c r="J42" s="15" t="n">
@@ -46480,7 +46480,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>09-Oct-2024 (Wed)</t>
+          <t>14-Oct-2024 (Mon)</t>
         </is>
       </c>
       <c r="G43" s="15" t="n">
@@ -46554,7 +46554,7 @@
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>07-Nov-2024 (Thu)</t>
+          <t>12-Nov-2024 (Tue)</t>
         </is>
       </c>
       <c r="G44" s="15" t="n">
@@ -46567,7 +46567,7 @@
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>20-Nov-2024 (Wed)</t>
+          <t>21-Nov-2024 (Thu)</t>
         </is>
       </c>
       <c r="J44" s="15" t="n">
@@ -46628,7 +46628,7 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>12-Dec-2024 (Thu)</t>
+          <t>16-Dec-2024 (Mon)</t>
         </is>
       </c>
       <c r="G45" s="15" t="n">
@@ -46641,7 +46641,7 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>26-Dec-2024 (Thu)</t>
+          <t>24-Dec-2024 (Tue)</t>
         </is>
       </c>
       <c r="J45" s="15" t="n">
@@ -46702,7 +46702,7 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>04-Oct-2024 (Fri)</t>
+          <t>09-Oct-2024 (Wed)</t>
         </is>
       </c>
       <c r="G46" s="15" t="n">
@@ -46715,7 +46715,7 @@
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>15-Oct-2024 (Tue)</t>
+          <t>17-Oct-2024 (Thu)</t>
         </is>
       </c>
       <c r="J46" s="15" t="n">
@@ -46776,7 +46776,7 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>30-Oct-2024 (Wed)</t>
+          <t>07-Nov-2024 (Thu)</t>
         </is>
       </c>
       <c r="G47" s="15" t="n">
@@ -46789,7 +46789,7 @@
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>19-Nov-2024 (Tue)</t>
+          <t>18-Nov-2024 (Mon)</t>
         </is>
       </c>
       <c r="J47" s="15" t="n">
@@ -46850,7 +46850,7 @@
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>08-Nov-2024 (Fri)</t>
+          <t>18-Nov-2024 (Mon)</t>
         </is>
       </c>
       <c r="G48" s="15" t="n">
@@ -46863,7 +46863,7 @@
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>22-Nov-2024 (Fri)</t>
+          <t>26-Nov-2024 (Tue)</t>
         </is>
       </c>
       <c r="J48" s="15" t="n">
@@ -46998,7 +46998,7 @@
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>11-Nov-2024 (Mon)</t>
+          <t>12-Nov-2024 (Tue)</t>
         </is>
       </c>
       <c r="G50" s="15" t="n">
@@ -47011,7 +47011,7 @@
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>22-Nov-2024 (Fri)</t>
+          <t>21-Nov-2024 (Thu)</t>
         </is>
       </c>
       <c r="J50" s="15" t="n">
@@ -47085,7 +47085,7 @@
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>12-Nov-2024 (Tue)</t>
+          <t>18-Nov-2024 (Mon)</t>
         </is>
       </c>
       <c r="J51" s="15" t="n">
@@ -47146,7 +47146,7 @@
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>17-Oct-2024 (Thu)</t>
+          <t>18-Oct-2024 (Fri)</t>
         </is>
       </c>
       <c r="G52" s="15" t="n">
@@ -47159,7 +47159,7 @@
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>29-Oct-2024 (Tue)</t>
+          <t>28-Oct-2024 (Mon)</t>
         </is>
       </c>
       <c r="J52" s="15" t="n">
@@ -47233,7 +47233,7 @@
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>20-Dec-2024 (Fri)</t>
+          <t>19-Dec-2024 (Thu)</t>
         </is>
       </c>
       <c r="J53" s="15" t="n">
@@ -47294,7 +47294,7 @@
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>07-Oct-2024 (Mon)</t>
+          <t>14-Oct-2024 (Mon)</t>
         </is>
       </c>
       <c r="G54" s="15" t="n">
@@ -47307,7 +47307,7 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>23-Oct-2024 (Wed)</t>
+          <t>22-Oct-2024 (Tue)</t>
         </is>
       </c>
       <c r="J54" s="15" t="n">
